--- a/mod_project/data_tables/qol_enchant_text.xlsx
+++ b/mod_project/data_tables/qol_enchant_text.xlsx
@@ -669,21 +669,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Max HP DOWN</t>
+          <t>Max HP -10%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Max HP -10%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>The DT2-2 wiki lists this one as unknown (-??%)</t>
@@ -2187,21 +2183,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Physical attack UP</t>
+          <t>Physical attack +4%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack +4%</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t>First game: stacks up to +50%</t>
@@ -2249,21 +2241,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Physical attack MiniUP</t>
+          <t>Physical attack +2%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack +2%</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>First game: stacks up to +50%</t>
@@ -2611,21 +2599,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Magic attack UP</t>
+          <t>Magic attack +4%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Magic attack +4%</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
           <t>First game: stacks up to +50%</t>
@@ -2673,21 +2657,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Magic attack MiniUP</t>
+          <t>Magic attack +2%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Magic attack +2%</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
           <t>First game: stacks up to +50%</t>
@@ -3235,21 +3215,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Enmity UP</t>
+          <t>Enmity +5%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>Enmity +5%</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3293,21 +3269,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Enmity DOWN</t>
+          <t>Enmity -5%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Enmity -5%</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3351,21 +3323,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Speed UP</t>
+          <t>Speed +10%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Speed +10%</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
           <t>DT2-2 player test: only five of them count</t>
@@ -3413,21 +3381,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Speed MiniUP</t>
+          <t>Speed +5%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Speed +5%</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3521,21 +3485,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Chant speed UP</t>
+          <t>Chant speed +20%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Chant speed +20%</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
           <t>DT2-2 player test: only three of them count</t>
@@ -3583,21 +3543,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Chant speed MiniUP</t>
+          <t>Chant speed +10%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Chant speed +10%</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3741,21 +3697,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Interruption rate DOWN</t>
+          <t>Interruption rate -6%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Interruption rate -6%</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -3799,21 +3751,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Interruption rate MiniDOWN</t>
+          <t>Interruption rate -3%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Interruption rate -3%</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -3857,21 +3805,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Interruption rate UP</t>
+          <t>Interruption rate +6%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>Interruption rate +6%</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4313,21 +4257,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Convert received damage into TP</t>
+          <t>Convert 5% of received damage into TP</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Convert 5% of received damage into TP</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
           <t>First game: at least 1 TP, also from poison and traps</t>
@@ -4425,21 +4365,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Fire magic buff</t>
+          <t>Fire magic +20%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Fire magic +20%</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
@@ -4487,21 +4423,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Water magic buff</t>
+          <t>Water magic +20%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>Water magic +20%</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
@@ -4549,21 +4481,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Wind magic buff</t>
+          <t>Wind magic +20%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Wind magic +20%</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
@@ -4611,21 +4539,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Earth magic buff</t>
+          <t>Earth magic +20%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>Earth magic +20%</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
@@ -4673,21 +4597,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Lightning magic buff</t>
+          <t>Lightning magic +20%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>Lightning magic +20%</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
@@ -4735,7 +4655,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +20</t>
+          <t>Fire resistance +20%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4789,7 +4709,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +10</t>
+          <t>Fire resistance +10%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4843,7 +4763,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance -20</t>
+          <t>Fire resistance -20%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4897,7 +4817,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +20</t>
+          <t>Water resistance +20%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4951,7 +4871,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +10</t>
+          <t>Water resistance +10%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -5005,7 +4925,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Water resistance -20</t>
+          <t>Water resistance -20%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -5059,7 +4979,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +20</t>
+          <t>Wind resistance +20%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -5113,7 +5033,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +10</t>
+          <t>Wind resistance +10%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -5167,7 +5087,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance -20</t>
+          <t>Wind resistance -20%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -5221,7 +5141,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +20</t>
+          <t>Earth resistance +20%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -5275,7 +5195,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +10</t>
+          <t>Earth resistance +10%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -5329,7 +5249,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance -20</t>
+          <t>Earth resistance -20%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -5383,7 +5303,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +20</t>
+          <t>Lightning resistance +20%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -5437,7 +5357,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +10</t>
+          <t>Lightning resistance +10%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -5491,7 +5411,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance -20</t>
+          <t>Lightning resistance -20%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -5541,7 +5461,7 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +50</t>
+          <t>Elemental resistance +50%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -5599,7 +5519,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +15</t>
+          <t>Elemental resistance +15%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5657,7 +5577,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +7</t>
+          <t>Elemental resistance +7%</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5715,7 +5635,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance -15</t>
+          <t>Elemental resistance -15%</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5773,7 +5693,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +20</t>
+          <t>Slash resistance +20%</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5827,7 +5747,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +10</t>
+          <t>Slash resistance +10%</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -5881,7 +5801,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance -20</t>
+          <t>Slash resistance -20%</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5935,7 +5855,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +20</t>
+          <t>Stab resistance +20%</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5989,7 +5909,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +10</t>
+          <t>Stab resistance +10%</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -6043,7 +5963,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance -20</t>
+          <t>Stab resistance -20%</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -6097,7 +6017,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +20</t>
+          <t>Bash resistance +20%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -6151,7 +6071,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +10</t>
+          <t>Bash resistance +10%</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -6205,7 +6125,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance -20</t>
+          <t>Bash resistance -20%</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -6255,7 +6175,7 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +25</t>
+          <t>Physical resistance +25%</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -6278,7 +6198,7 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +25)</t>
+          <t>contradicts dt22-wiki (Physical resistance +25%)</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6233,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +10</t>
+          <t>Physical resistance +10%</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -6336,7 +6256,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +10)</t>
+          <t>contradicts dt22-wiki (Physical resistance +10%)</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6291,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +5</t>
+          <t>Physical resistance +5%</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -6394,7 +6314,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +5)</t>
+          <t>contradicts dt22-wiki (Physical resistance +5%)</t>
         </is>
       </c>
     </row>
@@ -6429,21 +6349,17 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance DOWN</t>
+          <t>Physical resistance -10%</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>Physical resistance -10</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
           <t>Slash, stab and bash. The DT2-2 wiki lists this one as unknown (-??)</t>
@@ -6456,7 +6372,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical resistance -10)</t>
+          <t>contradicts dt2-wiki (Physical resistance -10%)</t>
         </is>
       </c>
     </row>
@@ -8131,21 +8047,17 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb lots of HP</t>
+          <t>Normal attacks absorb HP (50% of damage)</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks absorb 50% of damage as HP</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
           <t>First game: no effect on undead</t>
@@ -8193,21 +8105,17 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb HP</t>
+          <t>Normal attacks absorb HP (15% of damage)</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks absorb 15% of damage as HP</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
           <t>First game: no effect on undead</t>
@@ -8220,7 +8128,7 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Normal attacks absorb 15% of damage as HP)</t>
+          <t>contradicts dt2-wiki (Normal attacks absorb HP (15% of damage))</t>
         </is>
       </c>
     </row>
@@ -8251,21 +8159,17 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb lots of TP</t>
+          <t>Normal attacks absorb TP (20% of damage)</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks absorb 20% of damage as TP</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
           <t>First game: no effect on undead</t>
@@ -8313,21 +8217,17 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb TP</t>
+          <t>Normal attacks absorb TP (5% of damage)</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks absorb 5% of damage as TP</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
           <t>First game: no effect on undead</t>
@@ -8340,7 +8240,7 @@
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Normal attacks absorb 5% of damage as TP)</t>
+          <t>contradicts dt2-wiki (Normal attacks absorb TP (5% of damage))</t>
         </is>
       </c>
     </row>
@@ -8421,21 +8321,17 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Demons GrandUP</t>
+          <t>Physical attack vs. Demons +40%</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Demons +40%</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.4</t>
@@ -8483,21 +8379,17 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Demons UP</t>
+          <t>Physical attack vs. Demons +20%</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Demons +20%</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.2</t>
@@ -8541,21 +8433,17 @@
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Apparitions GrandUP</t>
+          <t>Physical attack vs. Apparitions +40%</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Apparitions +40%</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.4</t>
@@ -8603,21 +8491,17 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Apparitions UP</t>
+          <t>Physical attack vs. Apparitions +20%</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Apparitions +20%</t>
-        </is>
-      </c>
-      <c r="K151" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.2</t>
@@ -8661,21 +8545,17 @@
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Phys. attack vs. Magic Beings GrandUP</t>
+          <t>Phys. attack vs. Magic Beings +40%</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>Phys. attack vs. Magic Beings +40%</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.4</t>
@@ -8723,21 +8603,17 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Magic Beings UP</t>
+          <t>Physical attack vs. Magic Beings +20%</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Magic Beings +20%</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.2</t>
@@ -8781,21 +8657,17 @@
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Humans MegaUP</t>
+          <t>Physical attack vs. Humans +100%</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Humans +100%</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x2</t>
@@ -8839,21 +8711,17 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Humans GrandUP</t>
+          <t>Physical attack vs. Humans +40%</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Humans +40%</t>
-        </is>
-      </c>
-      <c r="K155" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.4</t>
@@ -8901,21 +8769,17 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Humans UP</t>
+          <t>Physical attack vs. Humans +20%</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Humans +20%</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.2</t>
@@ -8959,21 +8823,17 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Undead GrandUP</t>
+          <t>Physical attack vs. Undead +40%</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Undead +40%</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.4</t>
@@ -9021,21 +8881,17 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Undead UP</t>
+          <t>Physical attack vs. Undead +20%</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Undead +20%</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.2</t>
@@ -9079,21 +8935,17 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Dragons GrandUP</t>
+          <t>Physical attack vs. Dragons +40%</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Dragons +40%</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.4</t>
@@ -9141,21 +8993,17 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Dragons UP</t>
+          <t>Physical attack vs. Dragons +20%</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Dragons +20%</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.2</t>
@@ -9199,21 +9047,17 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Beasts GrandUP</t>
+          <t>Physical attack vs. Beasts +40%</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Beasts +40%</t>
-        </is>
-      </c>
-      <c r="K161" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.4</t>
@@ -9261,21 +9105,17 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Beasts UP</t>
+          <t>Physical attack vs. Beasts +20%</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Beasts +20%</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.2</t>
@@ -9319,21 +9159,17 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Fruit MegaUP</t>
+          <t>Physical attack vs. Fruit +100%</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Fruit +100%</t>
-        </is>
-      </c>
-      <c r="K163" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x2</t>
@@ -9381,21 +9217,17 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Fruit GrandUP</t>
+          <t>Physical attack vs. Fruit +50%</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Fruit +50%</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x1.5</t>
@@ -9623,21 +9455,17 @@
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Felines MegaUP</t>
+          <t>Physical attack vs. Felines +100%</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>Physical attack vs. Felines +100%</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>dt2-wiki</t>
         </is>
       </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
           <t>First game: physical damage x2</t>
@@ -13609,7 +13437,7 @@
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +100</t>
+          <t>Fire resistance +100%</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr"/>
@@ -13628,7 +13456,7 @@
       </c>
       <c r="N254" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Fire resistance +100)</t>
+          <t>contradicts dt22-wiki (Fire resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13487,7 @@
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +50</t>
+          <t>Fire resistance +50%</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr"/>
@@ -13713,7 +13541,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance -50</t>
+          <t>Fire resistance -50%</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
@@ -13732,7 +13560,7 @@
       </c>
       <c r="N256" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Fire resistance -50)</t>
+          <t>contradicts dt22-wiki (Fire resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -13763,7 +13591,7 @@
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +100</t>
+          <t>Water resistance +100%</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
@@ -13782,7 +13610,7 @@
       </c>
       <c r="N257" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Water resistance +100)</t>
+          <t>contradicts dt22-wiki (Water resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13641,7 @@
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +50</t>
+          <t>Water resistance +50%</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
@@ -13867,7 +13695,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Water resistance -50</t>
+          <t>Water resistance -50%</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
@@ -13886,7 +13714,7 @@
       </c>
       <c r="N259" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Water resistance -50)</t>
+          <t>contradicts dt22-wiki (Water resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13745,7 @@
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +100</t>
+          <t>Wind resistance +100%</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
@@ -13936,7 +13764,7 @@
       </c>
       <c r="N260" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Wind resistance +100)</t>
+          <t>contradicts dt22-wiki (Wind resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -13967,7 +13795,7 @@
       <c r="F261" s="2" t="inlineStr"/>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +50</t>
+          <t>Wind resistance +50%</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -14021,7 +13849,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance -50</t>
+          <t>Wind resistance -50%</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
@@ -14040,7 +13868,7 @@
       </c>
       <c r="N262" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Wind resistance -50)</t>
+          <t>contradicts dt22-wiki (Wind resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -14071,7 +13899,7 @@
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +100</t>
+          <t>Earth resistance +100%</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
@@ -14090,7 +13918,7 @@
       </c>
       <c r="N263" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Earth resistance +100)</t>
+          <t>contradicts dt22-wiki (Earth resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -14121,7 +13949,7 @@
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +50</t>
+          <t>Earth resistance +50%</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -14175,7 +14003,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance -50</t>
+          <t>Earth resistance -50%</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -14194,7 +14022,7 @@
       </c>
       <c r="N265" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Earth resistance -50)</t>
+          <t>contradicts dt22-wiki (Earth resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -14225,7 +14053,7 @@
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +100</t>
+          <t>Lightning resistance +100%</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -14244,7 +14072,7 @@
       </c>
       <c r="N266" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Lightning resistance +100)</t>
+          <t>contradicts dt22-wiki (Lightning resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -14275,7 +14103,7 @@
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +50</t>
+          <t>Lightning resistance +50%</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -14329,7 +14157,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance -50</t>
+          <t>Lightning resistance -50%</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -14348,7 +14176,7 @@
       </c>
       <c r="N268" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Lightning resistance -50)</t>
+          <t>contradicts dt22-wiki (Lightning resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14207,7 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +75</t>
+          <t>Elemental resistance +75%</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -14402,7 +14230,7 @@
       </c>
       <c r="N269" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Elemental resistance +75)</t>
+          <t>contradicts dt22-wiki (Elemental resistance +75%)</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14265,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance -30</t>
+          <t>Elemental resistance -30%</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -14491,7 +14319,7 @@
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +100</t>
+          <t>Slash resistance +100%</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -14510,7 +14338,7 @@
       </c>
       <c r="N271" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Slash resistance +100)</t>
+          <t>contradicts dt22-wiki (Slash resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14369,7 @@
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +50</t>
+          <t>Slash resistance +50%</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
@@ -14595,7 +14423,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance -50</t>
+          <t>Slash resistance -50%</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
@@ -14614,7 +14442,7 @@
       </c>
       <c r="N273" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Slash resistance -50)</t>
+          <t>contradicts dt22-wiki (Slash resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -14645,7 +14473,7 @@
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +100</t>
+          <t>Stab resistance +100%</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -14664,7 +14492,7 @@
       </c>
       <c r="N274" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Stab resistance +100)</t>
+          <t>contradicts dt22-wiki (Stab resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14523,7 @@
       <c r="F275" s="2" t="inlineStr"/>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +50</t>
+          <t>Stab resistance +50%</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -14749,7 +14577,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance -50</t>
+          <t>Stab resistance -50%</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -14768,7 +14596,7 @@
       </c>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Stab resistance -50)</t>
+          <t>contradicts dt22-wiki (Stab resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14627,7 @@
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +100</t>
+          <t>Bash resistance +100%</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
@@ -14818,7 +14646,7 @@
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Bash resistance +100)</t>
+          <t>contradicts dt22-wiki (Bash resistance +100%)</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14677,7 @@
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +50</t>
+          <t>Bash resistance +50%</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -14903,7 +14731,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance -50</t>
+          <t>Bash resistance -50%</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -14922,7 +14750,7 @@
       </c>
       <c r="N279" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Bash resistance -50)</t>
+          <t>contradicts dt22-wiki (Bash resistance -50%)</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14781,7 @@
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +50</t>
+          <t>Physical resistance +50%</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -14976,7 +14804,7 @@
       </c>
       <c r="N280" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +50)</t>
+          <t>contradicts dt22-wiki (Physical resistance +50%)</t>
         </is>
       </c>
     </row>
@@ -15011,7 +14839,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance -20</t>
+          <t>Physical resistance -20%</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
@@ -15034,7 +14862,7 @@
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance -20)</t>
+          <t>contradicts dt22-wiki (Physical resistance -20%)</t>
         </is>
       </c>
     </row>
@@ -15070,97 +14898,97 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>candidate from the first game only (vanilla name kept)</t>
+          <t>earlier build: agrees with dt2-wiki</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>earlier build: agrees with dt2-wiki</t>
+          <t>earlier build: agrees with dt22-wiki</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>earlier build: agrees with dt22-wiki</t>
+          <t>earlier build: contradicts dt2-wiki</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>earlier build: contradicts dt2-wiki</t>
+          <t>earlier build: contradicts dt22-wiki</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>earlier build: contradicts dt22-wiki</t>
+          <t>earlier build: figure without a source</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>earlier build: figure without a source</t>
+          <t>earlier build: reworded, no new figure</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>earlier build: reworded, no new figure</t>
+          <t>earlier build: unchanged</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>earlier build: unchanged</t>
+          <t>figure already in the vanilla name</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>figure already in the vanilla name</t>
+          <t>figure from dt2-wiki</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>figure from the guide of this game</t>
+          <t>figure from dt22-wiki</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -15236,12 +15064,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Japanese wiki of the first Dungeon Travelers 2, https://w.atwiki.jp/dungeon-travelers2/pages/200.html (same system, another game: candidate only)</t>
+          <t>Japanese wiki of the first Dungeon Travelers 2, https://w.atwiki.jp/dungeon-travelers2/pages/200.html (same system, another game: not confirmed for this one)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_enchant_text.xlsx
+++ b/mod_project/data_tables/qol_enchant_text.xlsx
@@ -569,14 +569,10 @@
           <t>At least +4. Max HP bonuses stack up to +50%</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Max HP +10%</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -627,14 +623,10 @@
           <t>At least +2. Max HP bonuses stack up to +50%</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Max HP +5%</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -685,14 +677,10 @@
           <t>The DT2-2 wiki lists this one as unknown (-??%)</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Max HP -10%</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -739,14 +727,10 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Max TP +10%</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -793,14 +777,10 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Max TP +5%</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -847,14 +827,10 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Max TP -10%</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -905,14 +881,10 @@
           <t>At least +4</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>ATK +10%</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -963,14 +935,10 @@
           <t>At least +2</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>ATK +5%</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1021,14 +989,10 @@
           <t>The first game's wiki lists -10%</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>ATK -10%</t>
-        </is>
-      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (ATK -5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1079,14 +1043,10 @@
           <t>At least +4</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>DEF +10%</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1137,14 +1097,10 @@
           <t>At least +2</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>DEF +5%</t>
-        </is>
-      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1195,14 +1151,10 @@
           <t>The first game's wiki lists -10%</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>DEF -10%</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (DEF -5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1205,10 @@
           <t>At least +4</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>INT +10%</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1311,14 +1259,10 @@
           <t>At least +2</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>INT +5%</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1369,14 +1313,10 @@
           <t>The first game's wiki lists -10%</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>INT -10%</t>
-        </is>
-      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (INT -5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1427,14 +1367,10 @@
           <t>At least +4</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>RES +10%</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1485,14 +1421,10 @@
           <t>At least +2</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>RES +5%</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1475,10 @@
           <t>The first game's wiki lists -10%</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>RES -10%</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (RES -5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1601,14 +1529,10 @@
           <t>At least +4</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>DEX +10%</t>
-        </is>
-      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1659,14 +1583,10 @@
           <t>At least +2</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>DEX +5%</t>
-        </is>
-      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1717,14 +1637,10 @@
           <t>The first game's wiki lists -10%</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>DEX -10%</t>
-        </is>
-      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (DEX -5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1775,14 +1691,10 @@
           <t>At least +4</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>AGI +10%</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1833,14 +1745,10 @@
           <t>At least +2</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>AGI +5%</t>
-        </is>
-      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1891,14 +1799,10 @@
           <t>The first game's wiki lists -10%</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>AGI -10%</t>
-        </is>
-      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (AGI -5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -1941,11 +1845,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>All stats +1</t>
-        </is>
-      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -1991,11 +1891,7 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>All stats +3</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -2041,11 +1937,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>All stats +6</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -2091,11 +1983,7 @@
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>All stats +9</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -2141,11 +2029,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>All stats +12</t>
-        </is>
-      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -2199,14 +2083,10 @@
           <t>First game: stacks up to +50%</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Phys ATK +10%</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack +4%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2257,14 +2137,10 @@
           <t>First game: stacks up to +50%</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Phys ATK +5%</t>
-        </is>
-      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack +2%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2307,14 +2183,10 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Phys Hit +10%</t>
-        </is>
-      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2357,14 +2229,10 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Phys Hit +5%</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2407,14 +2275,10 @@
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Phys DEF +10%</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2457,14 +2321,10 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Phys DEF +5%</t>
-        </is>
-      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2507,14 +2367,10 @@
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Phys Dodge +10%</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2557,14 +2413,10 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Phys Dodge +5%</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2615,14 +2467,10 @@
           <t>First game: stacks up to +50%</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Magic ATK +10%</t>
-        </is>
-      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Magic attack +4%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2673,14 +2521,10 @@
           <t>First game: stacks up to +50%</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Magic ATK +5%</t>
-        </is>
-      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Magic attack +2%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2723,14 +2567,10 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Magic Hit +10%</t>
-        </is>
-      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2773,14 +2613,10 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Magic Hit +5%</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2823,14 +2659,10 @@
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Magic DEF +10%</t>
-        </is>
-      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2873,14 +2705,10 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Magic DEF +5%</t>
-        </is>
-      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2923,14 +2751,10 @@
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Magic Dodge +10%</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -2973,14 +2797,10 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Magic Dodge +5%</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3023,14 +2843,10 @@
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>Crit Rate +10%</t>
-        </is>
-      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3073,14 +2889,10 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>Crit Rate +5%</t>
-        </is>
-      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3123,14 +2935,10 @@
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Enemy Crit -10%</t>
-        </is>
-      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3173,14 +2981,10 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Enemy Crit -5%</t>
-        </is>
-      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3227,14 +3031,10 @@
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Aggro/Enmity +25%</t>
-        </is>
-      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Enmity +5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3281,14 +3081,10 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>Aggro/Enmity -25%</t>
-        </is>
-      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Enmity -5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3339,14 +3135,10 @@
           <t>DT2-2 player test: only five of them count</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Action Speed +10%</t>
-        </is>
-      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3393,14 +3185,10 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Action Speed +5%</t>
-        </is>
-      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3443,14 +3231,10 @@
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>Action Speed -10%</t>
-        </is>
-      </c>
+      <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3501,14 +3285,10 @@
           <t>DT2-2 player test: only three of them count</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Chant Speed +15%</t>
-        </is>
-      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Chant speed +20%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3555,14 +3335,10 @@
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>Chant Speed +8%</t>
-        </is>
-      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Chant speed +10%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3605,14 +3381,10 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>Chant Speed -15%</t>
-        </is>
-      </c>
+      <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3655,14 +3427,10 @@
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>Interrupt Rate -90%</t>
-        </is>
-      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3709,14 +3477,10 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Interrupt Rate -50%</t>
-        </is>
-      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Interruption rate -6%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3763,14 +3527,10 @@
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>Interrupt Rate -25%</t>
-        </is>
-      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Interruption rate -3%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3817,14 +3577,10 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Interrupt Rate +25%</t>
-        </is>
-      </c>
+      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Interruption rate +6%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3867,14 +3623,10 @@
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>Interrupt Rate -75%</t>
-        </is>
-      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3925,14 +3677,10 @@
           <t>Damage reductions stack down to -25%</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>Phys Damage Taken -10%</t>
-        </is>
-      </c>
+      <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -3983,14 +3731,10 @@
           <t>Damage reductions stack down to -25%</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>Phys Damage Taken -5%</t>
-        </is>
-      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4041,14 +3785,10 @@
           <t>Damage reductions stack down to -25%</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>Magic Damage Taken -10%</t>
-        </is>
-      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4099,14 +3839,10 @@
           <t>Damage reductions stack down to -25%</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>Magic Damage Taken -5%</t>
-        </is>
-      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4157,14 +3893,10 @@
           <t>Physical and magic. Damage reductions stack down to -25%</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Damage Taken -10%</t>
-        </is>
-      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Received damage -8%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4215,14 +3947,10 @@
           <t>Physical and magic. Damage reductions stack down to -25%</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>Damage Taken -5%</t>
-        </is>
-      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Received damage -4%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4273,14 +4001,10 @@
           <t>First game: at least 1 TP, also from poison and traps</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>Damage -&gt; TP (10%)</t>
-        </is>
-      </c>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Convert 5% of received damage into TP)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4323,14 +4047,10 @@
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>Damage -&gt; TP (25%)</t>
-        </is>
-      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4381,14 +4101,10 @@
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>Fire Magic +15%</t>
-        </is>
-      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Fire magic +20%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4439,14 +4155,10 @@
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>Water Magic +15%</t>
-        </is>
-      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Water magic +20%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4497,14 +4209,10 @@
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>Wind Magic +15%</t>
-        </is>
-      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Wind magic +20%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4555,14 +4263,10 @@
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>Earth Magic +15%</t>
-        </is>
-      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Earth magic +20%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4613,14 +4317,10 @@
           <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Magic +15%</t>
-        </is>
-      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Lightning magic +20%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4355,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +20%</t>
+          <t>Fire resistance +20</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4667,14 +4367,10 @@
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>Fire Res +20</t>
-        </is>
-      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4405,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +10%</t>
+          <t>Fire resistance +10</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4721,14 +4417,10 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>Fire Res +10</t>
-        </is>
-      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4455,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance -20%</t>
+          <t>Fire resistance -20</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4775,14 +4467,10 @@
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>Fire Res -20</t>
-        </is>
-      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4505,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +20%</t>
+          <t>Water resistance +20</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4829,14 +4517,10 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>Water Res +20</t>
-        </is>
-      </c>
+      <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4555,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +10%</t>
+          <t>Water resistance +10</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4883,14 +4567,10 @@
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>Water Res +10</t>
-        </is>
-      </c>
+      <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4605,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Water resistance -20%</t>
+          <t>Water resistance -20</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4937,14 +4617,10 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>Water Res -20</t>
-        </is>
-      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4655,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +20%</t>
+          <t>Wind resistance +20</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4991,14 +4667,10 @@
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>Wind Res +20</t>
-        </is>
-      </c>
+      <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5033,7 +4705,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +10%</t>
+          <t>Wind resistance +10</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -5045,14 +4717,10 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>Wind Res +10</t>
-        </is>
-      </c>
+      <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5087,7 +4755,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance -20%</t>
+          <t>Wind resistance -20</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -5099,14 +4767,10 @@
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>Wind Res -20</t>
-        </is>
-      </c>
+      <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5141,7 +4805,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +20%</t>
+          <t>Earth resistance +20</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -5153,14 +4817,10 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>Earth Res +20</t>
-        </is>
-      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5195,7 +4855,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +10%</t>
+          <t>Earth resistance +10</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -5207,14 +4867,10 @@
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>Earth Res +10</t>
-        </is>
-      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5249,7 +4905,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance -20%</t>
+          <t>Earth resistance -20</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -5261,14 +4917,10 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>Earth Res -20</t>
-        </is>
-      </c>
+      <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5303,7 +4955,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +20%</t>
+          <t>Lightning resistance +20</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -5315,14 +4967,10 @@
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Res +20</t>
-        </is>
-      </c>
+      <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5005,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +10%</t>
+          <t>Lightning resistance +10</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -5369,14 +5017,10 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Res +10</t>
-        </is>
-      </c>
+      <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5055,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance -20%</t>
+          <t>Lightning resistance -20</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -5423,14 +5067,10 @@
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Res -20</t>
-        </is>
-      </c>
+      <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5101,7 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +50%</t>
+          <t>Elemental resistance +50</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -5477,14 +5117,10 @@
           <t>Each of the five elements</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>All Elem Res +50</t>
-        </is>
-      </c>
+      <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5155,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +15%</t>
+          <t>Elemental resistance +15</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -5535,14 +5171,10 @@
           <t>Each of the five elements</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>All Elem Res +15</t>
-        </is>
-      </c>
+      <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5209,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +7%</t>
+          <t>Elemental resistance +7</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -5593,14 +5225,10 @@
           <t>Each of the five elements</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>All Elem Res +7</t>
-        </is>
-      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5263,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance -15%</t>
+          <t>Elemental resistance -15</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -5651,14 +5279,10 @@
           <t>Each of the five elements</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>All Elem Res -15</t>
-        </is>
-      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5317,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +20%</t>
+          <t>Slash resistance +20</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5705,14 +5329,10 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>Slash Res +20</t>
-        </is>
-      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5367,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +10%</t>
+          <t>Slash resistance +10</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -5759,14 +5379,10 @@
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>Slash Res +10</t>
-        </is>
-      </c>
+      <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5417,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance -20%</t>
+          <t>Slash resistance -20</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -5813,14 +5429,10 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>Slash Res -20</t>
-        </is>
-      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5467,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +20%</t>
+          <t>Stab resistance +20</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5867,14 +5479,10 @@
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>Stab Res +20</t>
-        </is>
-      </c>
+      <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5517,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +10%</t>
+          <t>Stab resistance +10</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5921,14 +5529,10 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>Stab Res +10</t>
-        </is>
-      </c>
+      <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5567,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance -20%</t>
+          <t>Stab resistance -20</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5975,14 +5579,10 @@
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>Stab Res -20</t>
-        </is>
-      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6017,7 +5617,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +20%</t>
+          <t>Bash resistance +20</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -6029,14 +5629,10 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>Bash Res +20</t>
-        </is>
-      </c>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6071,7 +5667,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +10%</t>
+          <t>Bash resistance +10</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -6083,14 +5679,10 @@
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>Bash Res +10</t>
-        </is>
-      </c>
+      <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6125,7 +5717,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance -20%</t>
+          <t>Bash resistance -20</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -6137,14 +5729,10 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>Bash Res -20</t>
-        </is>
-      </c>
+      <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6175,7 +5763,7 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +25%</t>
+          <t>Physical resistance +25</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -6191,14 +5779,10 @@
           <t>Slash, stab and bash</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>All Phys Res +50</t>
-        </is>
-      </c>
+      <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +25%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6233,7 +5817,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +10%</t>
+          <t>Physical resistance +10</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -6249,14 +5833,10 @@
           <t>Slash, stab and bash</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>All Phys Res +15</t>
-        </is>
-      </c>
+      <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +10%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6291,7 +5871,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +5%</t>
+          <t>Physical resistance +5</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -6307,14 +5887,10 @@
           <t>Slash, stab and bash</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>All Phys Res +7</t>
-        </is>
-      </c>
+      <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +5%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6349,7 +5925,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance -10%</t>
+          <t>Physical resistance -10</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -6365,14 +5941,10 @@
           <t>Slash, stab and bash. The DT2-2 wiki lists this one as unknown (-??)</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>All Phys Res -15</t>
-        </is>
-      </c>
+      <c r="M108" s="2" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical resistance -10%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -6411,11 +5983,7 @@
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr">
-        <is>
-          <t>Nullify slash attacks</t>
-        </is>
-      </c>
+      <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6457,11 +6025,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr">
-        <is>
-          <t>Nullify stab attacks</t>
-        </is>
-      </c>
+      <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6503,11 +6067,7 @@
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr">
-        <is>
-          <t>Nullify bash attacks</t>
-        </is>
-      </c>
+      <c r="M111" s="2" t="inlineStr"/>
       <c r="N111" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6549,11 +6109,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr">
-        <is>
-          <t>Nullify physical attacks</t>
-        </is>
-      </c>
+      <c r="M112" s="2" t="inlineStr"/>
       <c r="N112" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6595,11 +6151,7 @@
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr">
-        <is>
-          <t>Nullify fire damage</t>
-        </is>
-      </c>
+      <c r="M113" s="2" t="inlineStr"/>
       <c r="N113" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6641,11 +6193,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr">
-        <is>
-          <t>Nullify water damage</t>
-        </is>
-      </c>
+      <c r="M114" s="2" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6687,11 +6235,7 @@
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t>Nullify wind damage</t>
-        </is>
-      </c>
+      <c r="M115" s="2" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6733,11 +6277,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr">
-        <is>
-          <t>Nullify earth damage</t>
-        </is>
-      </c>
+      <c r="M116" s="2" t="inlineStr"/>
       <c r="N116" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6779,11 +6319,7 @@
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="2" t="inlineStr">
-        <is>
-          <t>Nullify lightning damage</t>
-        </is>
-      </c>
+      <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6825,11 +6361,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr">
-        <is>
-          <t>Nullify stun</t>
-        </is>
-      </c>
+      <c r="M118" s="2" t="inlineStr"/>
       <c r="N118" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6871,11 +6403,7 @@
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="2" t="inlineStr">
-        <is>
-          <t>Nullify freeze</t>
-        </is>
-      </c>
+      <c r="M119" s="2" t="inlineStr"/>
       <c r="N119" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6917,11 +6445,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>Nullify poison</t>
-        </is>
-      </c>
+      <c r="M120" s="2" t="inlineStr"/>
       <c r="N120" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -6963,11 +6487,7 @@
       <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>Nullify sleep</t>
-        </is>
-      </c>
+      <c r="M121" s="2" t="inlineStr"/>
       <c r="N121" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7009,11 +6529,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr">
-        <is>
-          <t>Nullify silence</t>
-        </is>
-      </c>
+      <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7055,11 +6571,7 @@
       <c r="J123" s="2" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
-      <c r="M123" s="2" t="inlineStr">
-        <is>
-          <t>Nullify instakill</t>
-        </is>
-      </c>
+      <c r="M123" s="2" t="inlineStr"/>
       <c r="N123" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7101,11 +6613,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr">
-        <is>
-          <t>Nullify petrification</t>
-        </is>
-      </c>
+      <c r="M124" s="2" t="inlineStr"/>
       <c r="N124" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7147,11 +6655,7 @@
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="2" t="inlineStr">
-        <is>
-          <t>Nullify paralysis</t>
-        </is>
-      </c>
+      <c r="M125" s="2" t="inlineStr"/>
       <c r="N125" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7193,11 +6697,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr">
-        <is>
-          <t>Nullify all status ailments</t>
-        </is>
-      </c>
+      <c r="M126" s="2" t="inlineStr"/>
       <c r="N126" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7239,11 +6739,7 @@
       <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>Nullify gas traps</t>
-        </is>
-      </c>
+      <c r="M127" s="2" t="inlineStr"/>
       <c r="N127" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7285,11 +6781,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr">
-        <is>
-          <t>Nullify slow</t>
-        </is>
-      </c>
+      <c r="M128" s="2" t="inlineStr"/>
       <c r="N128" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -7339,14 +6831,10 @@
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="2" t="inlineStr">
-        <is>
-          <t>HP Regen +4%/turn</t>
-        </is>
-      </c>
+      <c r="M129" s="2" t="inlineStr"/>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7393,14 +6881,10 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
-      <c r="M130" s="2" t="inlineStr">
-        <is>
-          <t>HP Regen +2%/turn</t>
-        </is>
-      </c>
+      <c r="M130" s="2" t="inlineStr"/>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7447,14 +6931,10 @@
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="2" t="inlineStr">
-        <is>
-          <t>TP Regen +4/turn</t>
-        </is>
-      </c>
+      <c r="M131" s="2" t="inlineStr"/>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7501,14 +6981,10 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t>TP Regen +2/turn</t>
-        </is>
-      </c>
+      <c r="M132" s="2" t="inlineStr"/>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7555,14 +7031,10 @@
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="2" t="inlineStr">
-        <is>
-          <t>HP Regen +8%/turn</t>
-        </is>
-      </c>
+      <c r="M133" s="2" t="inlineStr"/>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7609,14 +7081,10 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr">
-        <is>
-          <t>TP Regen +6/turn</t>
-        </is>
-      </c>
+      <c r="M134" s="2" t="inlineStr"/>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7659,14 +7127,10 @@
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Poison chance (20%)</t>
-        </is>
-      </c>
+      <c r="M135" s="2" t="inlineStr"/>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7709,14 +7173,10 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Sleep chance (20%)</t>
-        </is>
-      </c>
+      <c r="M136" s="2" t="inlineStr"/>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7759,14 +7219,10 @@
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
-      <c r="M137" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Silence chance (20%)</t>
-        </is>
-      </c>
+      <c r="M137" s="2" t="inlineStr"/>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7809,14 +7265,10 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr"/>
-      <c r="M138" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Freeze chance (20%)</t>
-        </is>
-      </c>
+      <c r="M138" s="2" t="inlineStr"/>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7859,14 +7311,10 @@
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
-      <c r="M139" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Paralysis chance (20%)</t>
-        </is>
-      </c>
+      <c r="M139" s="2" t="inlineStr"/>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7909,14 +7357,10 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Stun chance (20%)</t>
-        </is>
-      </c>
+      <c r="M140" s="2" t="inlineStr"/>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -7959,14 +7403,10 @@
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr"/>
-      <c r="M141" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Petrify chance (15%)</t>
-        </is>
-      </c>
+      <c r="M141" s="2" t="inlineStr"/>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8009,14 +7449,10 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Instakill chance (15%)</t>
-        </is>
-      </c>
+      <c r="M142" s="2" t="inlineStr"/>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8063,14 +7499,10 @@
           <t>First game: no effect on undead</t>
         </is>
       </c>
-      <c r="M143" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: 50% HP Drain</t>
-        </is>
-      </c>
+      <c r="M143" s="2" t="inlineStr"/>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8121,14 +7553,10 @@
           <t>First game: no effect on undead</t>
         </is>
       </c>
-      <c r="M144" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: 20% HP Drain</t>
-        </is>
-      </c>
+      <c r="M144" s="2" t="inlineStr"/>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Normal attacks absorb HP (15% of damage))</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8175,14 +7603,10 @@
           <t>First game: no effect on undead</t>
         </is>
       </c>
-      <c r="M145" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: 20% TP Drain</t>
-        </is>
-      </c>
+      <c r="M145" s="2" t="inlineStr"/>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8233,14 +7657,10 @@
           <t>First game: no effect on undead</t>
         </is>
       </c>
-      <c r="M146" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: 10% TP Drain</t>
-        </is>
-      </c>
+      <c r="M146" s="2" t="inlineStr"/>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Normal attacks absorb TP (5% of damage))</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8283,14 +7703,10 @@
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
-      <c r="M147" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: Slow chance (15%)</t>
-        </is>
-      </c>
+      <c r="M147" s="2" t="inlineStr"/>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8337,14 +7753,10 @@
           <t>First game: physical damage x1.4</t>
         </is>
       </c>
-      <c r="M148" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Demons +50%</t>
-        </is>
-      </c>
+      <c r="M148" s="2" t="inlineStr"/>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack vs. Demons +40%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8395,14 +7807,10 @@
           <t>First game: physical damage x1.2</t>
         </is>
       </c>
-      <c r="M149" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Demons +20%</t>
-        </is>
-      </c>
+      <c r="M149" s="2" t="inlineStr"/>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8449,14 +7857,10 @@
           <t>First game: physical damage x1.4</t>
         </is>
       </c>
-      <c r="M150" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Apparitions +50%</t>
-        </is>
-      </c>
+      <c r="M150" s="2" t="inlineStr"/>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack vs. Apparitions +40%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8507,14 +7911,10 @@
           <t>First game: physical damage x1.2</t>
         </is>
       </c>
-      <c r="M151" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Apparitions +20%</t>
-        </is>
-      </c>
+      <c r="M151" s="2" t="inlineStr"/>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8561,14 +7961,10 @@
           <t>First game: physical damage x1.4</t>
         </is>
       </c>
-      <c r="M152" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Magic Beings +50%</t>
-        </is>
-      </c>
+      <c r="M152" s="2" t="inlineStr"/>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Phys. attack vs. Magic Beings +40%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8619,14 +8015,10 @@
           <t>First game: physical damage x1.2</t>
         </is>
       </c>
-      <c r="M153" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Magic Beings +20%</t>
-        </is>
-      </c>
+      <c r="M153" s="2" t="inlineStr"/>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8673,14 +8065,10 @@
           <t>First game: physical damage x2</t>
         </is>
       </c>
-      <c r="M154" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Humans +100%</t>
-        </is>
-      </c>
+      <c r="M154" s="2" t="inlineStr"/>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8727,14 +8115,10 @@
           <t>First game: physical damage x1.4</t>
         </is>
       </c>
-      <c r="M155" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Humans +50%</t>
-        </is>
-      </c>
+      <c r="M155" s="2" t="inlineStr"/>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack vs. Humans +40%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8785,14 +8169,10 @@
           <t>First game: physical damage x1.2</t>
         </is>
       </c>
-      <c r="M156" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Humans +20%</t>
-        </is>
-      </c>
+      <c r="M156" s="2" t="inlineStr"/>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8839,14 +8219,10 @@
           <t>First game: physical damage x1.4</t>
         </is>
       </c>
-      <c r="M157" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Undead +50%</t>
-        </is>
-      </c>
+      <c r="M157" s="2" t="inlineStr"/>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack vs. Undead +40%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8897,14 +8273,10 @@
           <t>First game: physical damage x1.2</t>
         </is>
       </c>
-      <c r="M158" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Undead +20%</t>
-        </is>
-      </c>
+      <c r="M158" s="2" t="inlineStr"/>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -8951,14 +8323,10 @@
           <t>First game: physical damage x1.4</t>
         </is>
       </c>
-      <c r="M159" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Dragons +50%</t>
-        </is>
-      </c>
+      <c r="M159" s="2" t="inlineStr"/>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack vs. Dragons +40%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9009,14 +8377,10 @@
           <t>First game: physical damage x1.2</t>
         </is>
       </c>
-      <c r="M160" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Dragons +20%</t>
-        </is>
-      </c>
+      <c r="M160" s="2" t="inlineStr"/>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9063,14 +8427,10 @@
           <t>First game: physical damage x1.4</t>
         </is>
       </c>
-      <c r="M161" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Beasts +50%</t>
-        </is>
-      </c>
+      <c r="M161" s="2" t="inlineStr"/>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt2-wiki (Physical attack vs. Beasts +40%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9121,14 +8481,10 @@
           <t>First game: physical damage x1.2</t>
         </is>
       </c>
-      <c r="M162" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Beasts +20%</t>
-        </is>
-      </c>
+      <c r="M162" s="2" t="inlineStr"/>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9175,14 +8531,10 @@
           <t>First game: physical damage x2</t>
         </is>
       </c>
-      <c r="M163" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Fruit +100%</t>
-        </is>
-      </c>
+      <c r="M163" s="2" t="inlineStr"/>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9233,14 +8585,10 @@
           <t>First game: physical damage x1.5</t>
         </is>
       </c>
-      <c r="M164" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Fruit +50%</t>
-        </is>
-      </c>
+      <c r="M164" s="2" t="inlineStr"/>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9279,11 +8627,7 @@
       <c r="J165" s="2" t="inlineStr"/>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr"/>
-      <c r="M165" s="2" t="inlineStr">
-        <is>
-          <t>Enemy HP and abilities are viewable</t>
-        </is>
-      </c>
+      <c r="M165" s="2" t="inlineStr"/>
       <c r="N165" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -9325,11 +8669,7 @@
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr">
-        <is>
-          <t>Fully recover HP after battle</t>
-        </is>
-      </c>
+      <c r="M166" s="2" t="inlineStr"/>
       <c r="N166" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -9371,11 +8711,7 @@
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr"/>
-      <c r="M167" s="2" t="inlineStr">
-        <is>
-          <t>Fully recover TP after battle</t>
-        </is>
-      </c>
+      <c r="M167" s="2" t="inlineStr"/>
       <c r="N167" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -9417,11 +8753,7 @@
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr">
-        <is>
-          <t>Pep is fixed at the max value</t>
-        </is>
-      </c>
+      <c r="M168" s="2" t="inlineStr"/>
       <c r="N168" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -9471,14 +8803,10 @@
           <t>First game: physical damage x2</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Felines +100%</t>
-        </is>
-      </c>
+      <c r="M169" s="2" t="inlineStr"/>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt2-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9517,14 +8845,10 @@
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr">
-        <is>
-          <t>Normal attacks: High Instakill chance (50%)</t>
-        </is>
-      </c>
+      <c r="M170" s="2" t="inlineStr"/>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9567,11 +8891,7 @@
       <c r="J171" s="2" t="inlineStr"/>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr"/>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>Pep will not drop below 100</t>
-        </is>
-      </c>
+      <c r="M171" s="2" t="inlineStr"/>
       <c r="N171" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -9617,11 +8937,7 @@
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
-      <c r="M172" s="2" t="inlineStr">
-        <is>
-          <t>Pep is fixed at the minimum value</t>
-        </is>
-      </c>
+      <c r="M172" s="2" t="inlineStr"/>
       <c r="N172" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -9663,14 +8979,10 @@
       <c r="J173" s="2" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Demons +100%</t>
-        </is>
-      </c>
+      <c r="M173" s="2" t="inlineStr"/>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9709,14 +9021,10 @@
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
-      <c r="M174" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Apparitions +100%</t>
-        </is>
-      </c>
+      <c r="M174" s="2" t="inlineStr"/>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9755,14 +9063,10 @@
       <c r="J175" s="2" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Magic Beings +100%</t>
-        </is>
-      </c>
+      <c r="M175" s="2" t="inlineStr"/>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9801,14 +9105,10 @@
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
-      <c r="M176" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Undead +100%</t>
-        </is>
-      </c>
+      <c r="M176" s="2" t="inlineStr"/>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9847,14 +9147,10 @@
       <c r="J177" s="2" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
-      <c r="M177" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Dragons +100%</t>
-        </is>
-      </c>
+      <c r="M177" s="2" t="inlineStr"/>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9893,14 +9189,10 @@
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
-      <c r="M178" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Beasts +100%</t>
-        </is>
-      </c>
+      <c r="M178" s="2" t="inlineStr"/>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9939,14 +9231,10 @@
       <c r="J179" s="2" t="inlineStr"/>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t>Physical ATK vs. Sea Creatures +100%</t>
-        </is>
-      </c>
+      <c r="M179" s="2" t="inlineStr"/>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -9985,14 +9273,10 @@
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
-      <c r="M180" s="2" t="inlineStr">
-        <is>
-          <t>Encounter Rate -25%</t>
-        </is>
-      </c>
+      <c r="M180" s="2" t="inlineStr"/>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10031,14 +9315,10 @@
       <c r="J181" s="2" t="inlineStr"/>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
-      <c r="M181" s="2" t="inlineStr">
-        <is>
-          <t>Encounter Rate -50%</t>
-        </is>
-      </c>
+      <c r="M181" s="2" t="inlineStr"/>
       <c r="N181" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10077,14 +9357,10 @@
       <c r="J182" s="2" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
-      <c r="M182" s="2" t="inlineStr">
-        <is>
-          <t>Encounter Rate +25%</t>
-        </is>
-      </c>
+      <c r="M182" s="2" t="inlineStr"/>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10123,14 +9399,10 @@
       <c r="J183" s="2" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
-      <c r="M183" s="2" t="inlineStr">
-        <is>
-          <t>Encounter Rate +50%</t>
-        </is>
-      </c>
+      <c r="M183" s="2" t="inlineStr"/>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10169,11 +9441,7 @@
       <c r="J184" s="2" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
-      <c r="M184" s="2" t="inlineStr">
-        <is>
-          <t>Recover 1 TP every 10 steps</t>
-        </is>
-      </c>
+      <c r="M184" s="2" t="inlineStr"/>
       <c r="N184" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -10215,14 +9483,10 @@
       <c r="J185" s="2" t="inlineStr"/>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
-      <c r="M185" s="2" t="inlineStr">
-        <is>
-          <t>Recover 3 TP / 10 steps</t>
-        </is>
-      </c>
+      <c r="M185" s="2" t="inlineStr"/>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10261,14 +9525,10 @@
       <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="2" t="inlineStr">
-        <is>
-          <t>ATK vs. Higher-Level Foes +25%</t>
-        </is>
-      </c>
+      <c r="M186" s="2" t="inlineStr"/>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10307,14 +9567,10 @@
       <c r="J187" s="2" t="inlineStr"/>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
-      <c r="M187" s="2" t="inlineStr">
-        <is>
-          <t>ATK vs. Lower-Level Foes +25%</t>
-        </is>
-      </c>
+      <c r="M187" s="2" t="inlineStr"/>
       <c r="N187" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10353,14 +9609,10 @@
       <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
-      <c r="M188" s="2" t="inlineStr">
-        <is>
-          <t>Front Row ATK +8%</t>
-        </is>
-      </c>
+      <c r="M188" s="2" t="inlineStr"/>
       <c r="N188" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10399,14 +9651,10 @@
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
-      <c r="M189" s="2" t="inlineStr">
-        <is>
-          <t>Front Row ATK/DEF +4%</t>
-        </is>
-      </c>
+      <c r="M189" s="2" t="inlineStr"/>
       <c r="N189" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10445,14 +9693,10 @@
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
-      <c r="M190" s="2" t="inlineStr">
-        <is>
-          <t>Back Row INT +8%</t>
-        </is>
-      </c>
+      <c r="M190" s="2" t="inlineStr"/>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10491,14 +9735,10 @@
       <c r="J191" s="2" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
-      <c r="M191" s="2" t="inlineStr">
-        <is>
-          <t>Back Row INT/RES +4%</t>
-        </is>
-      </c>
+      <c r="M191" s="2" t="inlineStr"/>
       <c r="N191" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10537,14 +9777,10 @@
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
-      <c r="M192" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Demons -5%</t>
-        </is>
-      </c>
+      <c r="M192" s="2" t="inlineStr"/>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10583,14 +9819,10 @@
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
-      <c r="M193" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Demons -10%</t>
-        </is>
-      </c>
+      <c r="M193" s="2" t="inlineStr"/>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10629,14 +9861,10 @@
       <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
-      <c r="M194" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Apparitions -5%</t>
-        </is>
-      </c>
+      <c r="M194" s="2" t="inlineStr"/>
       <c r="N194" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10675,14 +9903,10 @@
       <c r="J195" s="2" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
-      <c r="M195" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Apparitions -10%</t>
-        </is>
-      </c>
+      <c r="M195" s="2" t="inlineStr"/>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10721,14 +9945,10 @@
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
-      <c r="M196" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Magic Beings -5%</t>
-        </is>
-      </c>
+      <c r="M196" s="2" t="inlineStr"/>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10767,14 +9987,10 @@
       <c r="J197" s="2" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
-      <c r="M197" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Magic Beings -10%</t>
-        </is>
-      </c>
+      <c r="M197" s="2" t="inlineStr"/>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10813,14 +10029,10 @@
       <c r="J198" s="2" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
-      <c r="M198" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Humans -5%</t>
-        </is>
-      </c>
+      <c r="M198" s="2" t="inlineStr"/>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10859,14 +10071,10 @@
       <c r="J199" s="2" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
-      <c r="M199" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Humans -10%</t>
-        </is>
-      </c>
+      <c r="M199" s="2" t="inlineStr"/>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10905,14 +10113,10 @@
       <c r="J200" s="2" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
-      <c r="M200" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Undead -5%</t>
-        </is>
-      </c>
+      <c r="M200" s="2" t="inlineStr"/>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10951,14 +10155,10 @@
       <c r="J201" s="2" t="inlineStr"/>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
-      <c r="M201" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Undead -10%</t>
-        </is>
-      </c>
+      <c r="M201" s="2" t="inlineStr"/>
       <c r="N201" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -10997,14 +10197,10 @@
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
-      <c r="M202" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Dragons -5%</t>
-        </is>
-      </c>
+      <c r="M202" s="2" t="inlineStr"/>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11043,14 +10239,10 @@
       <c r="J203" s="2" t="inlineStr"/>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
-      <c r="M203" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Dragons -10%</t>
-        </is>
-      </c>
+      <c r="M203" s="2" t="inlineStr"/>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11089,14 +10281,10 @@
       <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
-      <c r="M204" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Beasts -5%</t>
-        </is>
-      </c>
+      <c r="M204" s="2" t="inlineStr"/>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11135,14 +10323,10 @@
       <c r="J205" s="2" t="inlineStr"/>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
-      <c r="M205" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Beasts -10%</t>
-        </is>
-      </c>
+      <c r="M205" s="2" t="inlineStr"/>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11181,14 +10365,10 @@
       <c r="J206" s="2" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr"/>
-      <c r="M206" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Fruit -5%</t>
-        </is>
-      </c>
+      <c r="M206" s="2" t="inlineStr"/>
       <c r="N206" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11227,14 +10407,10 @@
       <c r="J207" s="2" t="inlineStr"/>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr"/>
-      <c r="M207" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Fruit -10%</t>
-        </is>
-      </c>
+      <c r="M207" s="2" t="inlineStr"/>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11273,14 +10449,10 @@
       <c r="J208" s="2" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Therians -5%</t>
-        </is>
-      </c>
+      <c r="M208" s="2" t="inlineStr"/>
       <c r="N208" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11319,14 +10491,10 @@
       <c r="J209" s="2" t="inlineStr"/>
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr"/>
-      <c r="M209" s="2" t="inlineStr">
-        <is>
-          <t>Damage from Therians -10%</t>
-        </is>
-      </c>
+      <c r="M209" s="2" t="inlineStr"/>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11365,14 +10533,10 @@
       <c r="J210" s="2" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr">
-        <is>
-          <t>Technique TP Cost -10%</t>
-        </is>
-      </c>
+      <c r="M210" s="2" t="inlineStr"/>
       <c r="N210" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11411,14 +10575,10 @@
       <c r="J211" s="2" t="inlineStr"/>
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr"/>
-      <c r="M211" s="2" t="inlineStr">
-        <is>
-          <t>Technique TP Cost -25%</t>
-        </is>
-      </c>
+      <c r="M211" s="2" t="inlineStr"/>
       <c r="N211" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11457,14 +10617,10 @@
       <c r="J212" s="2" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr"/>
-      <c r="M212" s="2" t="inlineStr">
-        <is>
-          <t>Spell TP Cost -10%</t>
-        </is>
-      </c>
+      <c r="M212" s="2" t="inlineStr"/>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11503,14 +10659,10 @@
       <c r="J213" s="2" t="inlineStr"/>
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr"/>
-      <c r="M213" s="2" t="inlineStr">
-        <is>
-          <t>Spell TP Cost -25%</t>
-        </is>
-      </c>
+      <c r="M213" s="2" t="inlineStr"/>
       <c r="N213" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11549,14 +10701,10 @@
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr"/>
-      <c r="M214" s="2" t="inlineStr">
-        <is>
-          <t>Fire Attack for all allies &amp; foes +25%</t>
-        </is>
-      </c>
+      <c r="M214" s="2" t="inlineStr"/>
       <c r="N214" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11595,14 +10743,10 @@
       <c r="J215" s="2" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr"/>
-      <c r="M215" s="2" t="inlineStr">
-        <is>
-          <t>Water Attack for all allies &amp; foes +25%</t>
-        </is>
-      </c>
+      <c r="M215" s="2" t="inlineStr"/>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11641,14 +10785,10 @@
       <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr"/>
-      <c r="M216" s="2" t="inlineStr">
-        <is>
-          <t>Wind Attack for all allies &amp; foes +25%</t>
-        </is>
-      </c>
+      <c r="M216" s="2" t="inlineStr"/>
       <c r="N216" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11687,14 +10827,10 @@
       <c r="J217" s="2" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr"/>
-      <c r="M217" s="2" t="inlineStr">
-        <is>
-          <t>Earth Attack for all allies &amp; foes +25%</t>
-        </is>
-      </c>
+      <c r="M217" s="2" t="inlineStr"/>
       <c r="N217" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11733,14 +10869,10 @@
       <c r="J218" s="2" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr"/>
-      <c r="M218" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Attack for all allies &amp; foes +25%</t>
-        </is>
-      </c>
+      <c r="M218" s="2" t="inlineStr"/>
       <c r="N218" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11779,14 +10911,10 @@
       <c r="J219" s="2" t="inlineStr"/>
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr"/>
-      <c r="M219" s="2" t="inlineStr">
-        <is>
-          <t>Defending HP Regen +10%</t>
-        </is>
-      </c>
+      <c r="M219" s="2" t="inlineStr"/>
       <c r="N219" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11833,14 +10961,10 @@
           <t>Page 40, grand sealbook Kaguya</t>
         </is>
       </c>
-      <c r="M220" s="2" t="inlineStr">
-        <is>
-          <t>Treasure Chest Item Level +1</t>
-        </is>
-      </c>
+      <c r="M220" s="2" t="inlineStr"/>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Equipment from treasure boxes: level +2)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11879,14 +11003,10 @@
       <c r="J221" s="2" t="inlineStr"/>
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr"/>
-      <c r="M221" s="2" t="inlineStr">
-        <is>
-          <t>Wandering Shop Encounter Rate +50%</t>
-        </is>
-      </c>
+      <c r="M221" s="2" t="inlineStr"/>
       <c r="N221" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11925,14 +11045,10 @@
       <c r="J222" s="2" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr"/>
-      <c r="M222" s="2" t="inlineStr">
-        <is>
-          <t>Non-Gas Trap Damage -90%</t>
-        </is>
-      </c>
+      <c r="M222" s="2" t="inlineStr"/>
       <c r="N222" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -11971,14 +11087,10 @@
       <c r="J223" s="2" t="inlineStr"/>
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr"/>
-      <c r="M223" s="2" t="inlineStr">
-        <is>
-          <t>Joint Skill Damage +25%</t>
-        </is>
-      </c>
+      <c r="M223" s="2" t="inlineStr"/>
       <c r="N223" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12017,14 +11129,10 @@
       <c r="J224" s="2" t="inlineStr"/>
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="2" t="inlineStr">
-        <is>
-          <t>Escape Chance +25%</t>
-        </is>
-      </c>
+      <c r="M224" s="2" t="inlineStr"/>
       <c r="N224" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12063,14 +11171,10 @@
       <c r="J225" s="2" t="inlineStr"/>
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr"/>
-      <c r="M225" s="2" t="inlineStr">
-        <is>
-          <t>Unarmed Action Speed: A-Rank</t>
-        </is>
-      </c>
+      <c r="M225" s="2" t="inlineStr"/>
       <c r="N225" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12109,14 +11213,10 @@
       <c r="J226" s="2" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr"/>
-      <c r="M226" s="2" t="inlineStr">
-        <is>
-          <t>Class Weapon Modifier +2%</t>
-        </is>
-      </c>
+      <c r="M226" s="2" t="inlineStr"/>
       <c r="N226" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12155,14 +11255,10 @@
       <c r="J227" s="2" t="inlineStr"/>
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr"/>
-      <c r="M227" s="2" t="inlineStr">
-        <is>
-          <t>Ailment Natural Recovery Rate +50%</t>
-        </is>
-      </c>
+      <c r="M227" s="2" t="inlineStr"/>
       <c r="N227" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12201,14 +11297,10 @@
       <c r="J228" s="2" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr"/>
-      <c r="M228" s="2" t="inlineStr">
-        <is>
-          <t>Pep Decrease Rate -50%</t>
-        </is>
-      </c>
+      <c r="M228" s="2" t="inlineStr"/>
       <c r="N228" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12255,14 +11347,10 @@
           <t>Page 105, player test of grand sealbook Heket: 110% / 120% / 130% / 140% with 4 / 3 / 2 / 1 members</t>
         </is>
       </c>
-      <c r="M229" s="2" t="inlineStr">
-        <is>
-          <t>Damage +100%/empty party slot</t>
-        </is>
-      </c>
+      <c r="M229" s="2" t="inlineStr"/>
       <c r="N229" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Damage +10% per missing party member)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12301,14 +11389,10 @@
       <c r="J230" s="2" t="inlineStr"/>
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr"/>
-      <c r="M230" s="2" t="inlineStr">
-        <is>
-          <t>Crit Rate +10%</t>
-        </is>
-      </c>
+      <c r="M230" s="2" t="inlineStr"/>
       <c r="N230" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12347,14 +11431,10 @@
       <c r="J231" s="2" t="inlineStr"/>
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr">
-        <is>
-          <t>Trap Trigger Rate -50%</t>
-        </is>
-      </c>
+      <c r="M231" s="2" t="inlineStr"/>
       <c r="N231" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12401,14 +11481,10 @@
           <t>Page 40, grand sealbook Dragon Puppy</t>
         </is>
       </c>
-      <c r="M232" s="2" t="inlineStr">
-        <is>
-          <t>Higher-Level Enemy EXP +50%</t>
-        </is>
-      </c>
+      <c r="M232" s="2" t="inlineStr"/>
       <c r="N232" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (EXP from higher-level enemies +15%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12447,14 +11523,10 @@
       <c r="J233" s="2" t="inlineStr"/>
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr"/>
-      <c r="M233" s="2" t="inlineStr">
-        <is>
-          <t>Damage at Max HP +10%</t>
-        </is>
-      </c>
+      <c r="M233" s="2" t="inlineStr"/>
       <c r="N233" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12493,14 +11565,10 @@
       <c r="J234" s="2" t="inlineStr"/>
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr"/>
-      <c r="M234" s="2" t="inlineStr">
-        <is>
-          <t>Missed Spell Damage Penalty -50%</t>
-        </is>
-      </c>
+      <c r="M234" s="2" t="inlineStr"/>
       <c r="N234" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12539,11 +11607,7 @@
       <c r="J235" s="2" t="inlineStr"/>
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr"/>
-      <c r="M235" s="2" t="inlineStr">
-        <is>
-          <t>Double EXP</t>
-        </is>
-      </c>
+      <c r="M235" s="2" t="inlineStr"/>
       <c r="N235" s="2" t="inlineStr">
         <is>
           <t>unchanged</t>
@@ -12589,14 +11653,10 @@
       <c r="J236" s="2" t="inlineStr"/>
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr"/>
-      <c r="M236" s="2" t="inlineStr">
-        <is>
-          <t>Equipment Drop Rate +25%</t>
-        </is>
-      </c>
+      <c r="M236" s="2" t="inlineStr"/>
       <c r="N236" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12635,14 +11695,10 @@
       <c r="J237" s="2" t="inlineStr"/>
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr"/>
-      <c r="M237" s="2" t="inlineStr">
-        <is>
-          <t>Damage vs. Ailment Foes +25%</t>
-        </is>
-      </c>
+      <c r="M237" s="2" t="inlineStr"/>
       <c r="N237" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12681,14 +11737,10 @@
       <c r="J238" s="2" t="inlineStr"/>
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr"/>
-      <c r="M238" s="2" t="inlineStr">
-        <is>
-          <t>Back Row DEX/AGI +2%</t>
-        </is>
-      </c>
+      <c r="M238" s="2" t="inlineStr"/>
       <c r="N238" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12727,14 +11779,10 @@
       <c r="J239" s="2" t="inlineStr"/>
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr"/>
-      <c r="M239" s="2" t="inlineStr">
-        <is>
-          <t>Joint Skill Damage +50%</t>
-        </is>
-      </c>
+      <c r="M239" s="2" t="inlineStr"/>
       <c r="N239" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12773,14 +11821,10 @@
       <c r="J240" s="2" t="inlineStr"/>
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr"/>
-      <c r="M240" s="2" t="inlineStr">
-        <is>
-          <t>Chest Mimic Appearance Rate +50%</t>
-        </is>
-      </c>
+      <c r="M240" s="2" t="inlineStr"/>
       <c r="N240" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12819,14 +11863,10 @@
       <c r="J241" s="2" t="inlineStr"/>
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr"/>
-      <c r="M241" s="2" t="inlineStr">
-        <is>
-          <t>Defending TP Regen +10</t>
-        </is>
-      </c>
+      <c r="M241" s="2" t="inlineStr"/>
       <c r="N241" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12865,14 +11905,10 @@
       <c r="J242" s="2" t="inlineStr"/>
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr"/>
-      <c r="M242" s="2" t="inlineStr">
-        <is>
-          <t>Unique Skill Level +1</t>
-        </is>
-      </c>
+      <c r="M242" s="2" t="inlineStr"/>
       <c r="N242" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12911,14 +11947,10 @@
       <c r="J243" s="2" t="inlineStr"/>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr"/>
-      <c r="M243" s="2" t="inlineStr">
-        <is>
-          <t>Food Affinity Bonus/Penalty x2</t>
-        </is>
-      </c>
+      <c r="M243" s="2" t="inlineStr"/>
       <c r="N243" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -12957,14 +11989,10 @@
       <c r="J244" s="2" t="inlineStr"/>
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr"/>
-      <c r="M244" s="2" t="inlineStr">
-        <is>
-          <t>Mercenary Buddy Stats +10%</t>
-        </is>
-      </c>
+      <c r="M244" s="2" t="inlineStr"/>
       <c r="N244" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13003,14 +12031,10 @@
       <c r="J245" s="2" t="inlineStr"/>
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr"/>
-      <c r="M245" s="2" t="inlineStr">
-        <is>
-          <t>Turn Start Full HP Recovery (10%)</t>
-        </is>
-      </c>
+      <c r="M245" s="2" t="inlineStr"/>
       <c r="N245" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13049,14 +12073,10 @@
       <c r="J246" s="2" t="inlineStr"/>
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr"/>
-      <c r="M246" s="2" t="inlineStr">
-        <is>
-          <t>Mercenary Buddy Stats +30</t>
-        </is>
-      </c>
+      <c r="M246" s="2" t="inlineStr"/>
       <c r="N246" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13095,14 +12115,10 @@
       <c r="J247" s="2" t="inlineStr"/>
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr"/>
-      <c r="M247" s="2" t="inlineStr">
-        <is>
-          <t>Fast Spell Cast (Instant Cast chance)</t>
-        </is>
-      </c>
+      <c r="M247" s="2" t="inlineStr"/>
       <c r="N247" s="2" t="inlineStr">
         <is>
-          <t>reworded, no new figure</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13153,14 +12169,10 @@
           <t>Carol +20%, Chorale +2, every other song +2%</t>
         </is>
       </c>
-      <c r="M248" s="2" t="inlineStr">
-        <is>
-          <t>Song Potency +20% (Carol/Chorale etc.)</t>
-        </is>
-      </c>
+      <c r="M248" s="2" t="inlineStr"/>
       <c r="N248" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Songs +2% (Carol +20%, Chorale +2))</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13207,14 +12219,10 @@
           <t>Carol +10%, Chorale +1, every other song +1%</t>
         </is>
       </c>
-      <c r="M249" s="2" t="inlineStr">
-        <is>
-          <t>Song Potency +10%</t>
-        </is>
-      </c>
+      <c r="M249" s="2" t="inlineStr"/>
       <c r="N249" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Songs +1% (Carol +10%, Chorale +1))</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13257,14 +12265,10 @@
       <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr"/>
-      <c r="M250" s="2" t="inlineStr">
-        <is>
-          <t>Dance Potency +20%</t>
-        </is>
-      </c>
+      <c r="M250" s="2" t="inlineStr"/>
       <c r="N250" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13303,14 +12307,10 @@
       <c r="J251" s="2" t="inlineStr"/>
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr"/>
-      <c r="M251" s="2" t="inlineStr">
-        <is>
-          <t>Dance Potency +10%</t>
-        </is>
-      </c>
+      <c r="M251" s="2" t="inlineStr"/>
       <c r="N251" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13353,14 +12353,10 @@
       <c r="J252" s="2" t="inlineStr"/>
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr"/>
-      <c r="M252" s="2" t="inlineStr">
-        <is>
-          <t>Doll Potency +20%</t>
-        </is>
-      </c>
+      <c r="M252" s="2" t="inlineStr"/>
       <c r="N252" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13399,14 +12395,10 @@
       <c r="J253" s="2" t="inlineStr"/>
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr"/>
-      <c r="M253" s="2" t="inlineStr">
-        <is>
-          <t>Doll Potency +10%</t>
-        </is>
-      </c>
+      <c r="M253" s="2" t="inlineStr"/>
       <c r="N253" s="2" t="inlineStr">
         <is>
-          <t>figure without a source</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13437,7 +12429,7 @@
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +100%</t>
+          <t>Fire resistance +100</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr"/>
@@ -13449,14 +12441,10 @@
       <c r="J254" s="2" t="inlineStr"/>
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr"/>
-      <c r="M254" s="2" t="inlineStr">
-        <is>
-          <t>Fire Res +30</t>
-        </is>
-      </c>
+      <c r="M254" s="2" t="inlineStr"/>
       <c r="N254" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Fire resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13487,7 +12475,7 @@
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance +50%</t>
+          <t>Fire resistance +50</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr"/>
@@ -13499,14 +12487,10 @@
       <c r="J255" s="2" t="inlineStr"/>
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr"/>
-      <c r="M255" s="2" t="inlineStr">
-        <is>
-          <t>Fire Res +50</t>
-        </is>
-      </c>
+      <c r="M255" s="2" t="inlineStr"/>
       <c r="N255" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13541,7 +12525,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Fire resistance -50%</t>
+          <t>Fire resistance -50</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
@@ -13553,14 +12537,10 @@
       <c r="J256" s="2" t="inlineStr"/>
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr"/>
-      <c r="M256" s="2" t="inlineStr">
-        <is>
-          <t>Fire Res -40</t>
-        </is>
-      </c>
+      <c r="M256" s="2" t="inlineStr"/>
       <c r="N256" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Fire resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13591,7 +12571,7 @@
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +100%</t>
+          <t>Water resistance +100</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
@@ -13603,14 +12583,10 @@
       <c r="J257" s="2" t="inlineStr"/>
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr"/>
-      <c r="M257" s="2" t="inlineStr">
-        <is>
-          <t>Water Res +30</t>
-        </is>
-      </c>
+      <c r="M257" s="2" t="inlineStr"/>
       <c r="N257" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Water resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13641,7 +12617,7 @@
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Water resistance +50%</t>
+          <t>Water resistance +50</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
@@ -13653,14 +12629,10 @@
       <c r="J258" s="2" t="inlineStr"/>
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr"/>
-      <c r="M258" s="2" t="inlineStr">
-        <is>
-          <t>Water Res +50</t>
-        </is>
-      </c>
+      <c r="M258" s="2" t="inlineStr"/>
       <c r="N258" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13695,7 +12667,7 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Water resistance -50%</t>
+          <t>Water resistance -50</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr"/>
@@ -13707,14 +12679,10 @@
       <c r="J259" s="2" t="inlineStr"/>
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr"/>
-      <c r="M259" s="2" t="inlineStr">
-        <is>
-          <t>Water Res -40</t>
-        </is>
-      </c>
+      <c r="M259" s="2" t="inlineStr"/>
       <c r="N259" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Water resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13745,7 +12713,7 @@
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +100%</t>
+          <t>Wind resistance +100</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
@@ -13757,14 +12725,10 @@
       <c r="J260" s="2" t="inlineStr"/>
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr"/>
-      <c r="M260" s="2" t="inlineStr">
-        <is>
-          <t>Wind Res +30</t>
-        </is>
-      </c>
+      <c r="M260" s="2" t="inlineStr"/>
       <c r="N260" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Wind resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13795,7 +12759,7 @@
       <c r="F261" s="2" t="inlineStr"/>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance +50%</t>
+          <t>Wind resistance +50</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr"/>
@@ -13807,14 +12771,10 @@
       <c r="J261" s="2" t="inlineStr"/>
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr"/>
-      <c r="M261" s="2" t="inlineStr">
-        <is>
-          <t>Wind Res +50</t>
-        </is>
-      </c>
+      <c r="M261" s="2" t="inlineStr"/>
       <c r="N261" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13849,7 +12809,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Wind resistance -50%</t>
+          <t>Wind resistance -50</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
@@ -13861,14 +12821,10 @@
       <c r="J262" s="2" t="inlineStr"/>
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr"/>
-      <c r="M262" s="2" t="inlineStr">
-        <is>
-          <t>Wind Res -40</t>
-        </is>
-      </c>
+      <c r="M262" s="2" t="inlineStr"/>
       <c r="N262" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Wind resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13899,7 +12855,7 @@
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +100%</t>
+          <t>Earth resistance +100</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
@@ -13911,14 +12867,10 @@
       <c r="J263" s="2" t="inlineStr"/>
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr"/>
-      <c r="M263" s="2" t="inlineStr">
-        <is>
-          <t>Earth Res +30</t>
-        </is>
-      </c>
+      <c r="M263" s="2" t="inlineStr"/>
       <c r="N263" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Earth resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -13949,7 +12901,7 @@
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance +50%</t>
+          <t>Earth resistance +50</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
@@ -13961,14 +12913,10 @@
       <c r="J264" s="2" t="inlineStr"/>
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr"/>
-      <c r="M264" s="2" t="inlineStr">
-        <is>
-          <t>Earth Res +50</t>
-        </is>
-      </c>
+      <c r="M264" s="2" t="inlineStr"/>
       <c r="N264" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14003,7 +12951,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Earth resistance -50%</t>
+          <t>Earth resistance -50</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr"/>
@@ -14015,14 +12963,10 @@
       <c r="J265" s="2" t="inlineStr"/>
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr"/>
-      <c r="M265" s="2" t="inlineStr">
-        <is>
-          <t>Earth Res -40</t>
-        </is>
-      </c>
+      <c r="M265" s="2" t="inlineStr"/>
       <c r="N265" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Earth resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14053,7 +12997,7 @@
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +100%</t>
+          <t>Lightning resistance +100</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
@@ -14065,14 +13009,10 @@
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr"/>
-      <c r="M266" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Res +30</t>
-        </is>
-      </c>
+      <c r="M266" s="2" t="inlineStr"/>
       <c r="N266" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Lightning resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14103,7 +13043,7 @@
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance +50%</t>
+          <t>Lightning resistance +50</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr"/>
@@ -14115,14 +13055,10 @@
       <c r="J267" s="2" t="inlineStr"/>
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr"/>
-      <c r="M267" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Res +50</t>
-        </is>
-      </c>
+      <c r="M267" s="2" t="inlineStr"/>
       <c r="N267" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14157,7 +13093,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Lightning resistance -50%</t>
+          <t>Lightning resistance -50</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
@@ -14169,14 +13105,10 @@
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr"/>
-      <c r="M268" s="2" t="inlineStr">
-        <is>
-          <t>Lightning Res -40</t>
-        </is>
-      </c>
+      <c r="M268" s="2" t="inlineStr"/>
       <c r="N268" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Lightning resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14207,7 +13139,7 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance +75%</t>
+          <t>Elemental resistance +75</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr"/>
@@ -14223,14 +13155,10 @@
           <t>Each of the five elements</t>
         </is>
       </c>
-      <c r="M269" s="2" t="inlineStr">
-        <is>
-          <t>All Elem Res +30</t>
-        </is>
-      </c>
+      <c r="M269" s="2" t="inlineStr"/>
       <c r="N269" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Elemental resistance +75%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14265,7 +13193,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Elemental resistance -30%</t>
+          <t>Elemental resistance -30</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr"/>
@@ -14281,14 +13209,10 @@
           <t>Each of the five elements</t>
         </is>
       </c>
-      <c r="M270" s="2" t="inlineStr">
-        <is>
-          <t>All Elem Res -30</t>
-        </is>
-      </c>
+      <c r="M270" s="2" t="inlineStr"/>
       <c r="N270" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14319,7 +13243,7 @@
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +100%</t>
+          <t>Slash resistance +100</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr"/>
@@ -14331,14 +13255,10 @@
       <c r="J271" s="2" t="inlineStr"/>
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr"/>
-      <c r="M271" s="2" t="inlineStr">
-        <is>
-          <t>Slash Res +30</t>
-        </is>
-      </c>
+      <c r="M271" s="2" t="inlineStr"/>
       <c r="N271" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Slash resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14369,7 +13289,7 @@
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance +50%</t>
+          <t>Slash resistance +50</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
@@ -14381,14 +13301,10 @@
       <c r="J272" s="2" t="inlineStr"/>
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr"/>
-      <c r="M272" s="2" t="inlineStr">
-        <is>
-          <t>Slash Res +50</t>
-        </is>
-      </c>
+      <c r="M272" s="2" t="inlineStr"/>
       <c r="N272" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14423,7 +13339,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Slash resistance -50%</t>
+          <t>Slash resistance -50</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
@@ -14435,14 +13351,10 @@
       <c r="J273" s="2" t="inlineStr"/>
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr"/>
-      <c r="M273" s="2" t="inlineStr">
-        <is>
-          <t>Slash Res -40</t>
-        </is>
-      </c>
+      <c r="M273" s="2" t="inlineStr"/>
       <c r="N273" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Slash resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14473,7 +13385,7 @@
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +100%</t>
+          <t>Stab resistance +100</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
@@ -14485,14 +13397,10 @@
       <c r="J274" s="2" t="inlineStr"/>
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr"/>
-      <c r="M274" s="2" t="inlineStr">
-        <is>
-          <t>Stab Res +30</t>
-        </is>
-      </c>
+      <c r="M274" s="2" t="inlineStr"/>
       <c r="N274" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Stab resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14523,7 +13431,7 @@
       <c r="F275" s="2" t="inlineStr"/>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance +50%</t>
+          <t>Stab resistance +50</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
@@ -14535,14 +13443,10 @@
       <c r="J275" s="2" t="inlineStr"/>
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr"/>
-      <c r="M275" s="2" t="inlineStr">
-        <is>
-          <t>Stab Res +50</t>
-        </is>
-      </c>
+      <c r="M275" s="2" t="inlineStr"/>
       <c r="N275" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14577,7 +13481,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Stab resistance -50%</t>
+          <t>Stab resistance -50</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
@@ -14589,14 +13493,10 @@
       <c r="J276" s="2" t="inlineStr"/>
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr"/>
-      <c r="M276" s="2" t="inlineStr">
-        <is>
-          <t>Stab Res -40</t>
-        </is>
-      </c>
+      <c r="M276" s="2" t="inlineStr"/>
       <c r="N276" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Stab resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14627,7 +13527,7 @@
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +100%</t>
+          <t>Bash resistance +100</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr"/>
@@ -14639,14 +13539,10 @@
       <c r="J277" s="2" t="inlineStr"/>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
-      <c r="M277" s="2" t="inlineStr">
-        <is>
-          <t>Bash Res +30</t>
-        </is>
-      </c>
+      <c r="M277" s="2" t="inlineStr"/>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Bash resistance +100%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14677,7 +13573,7 @@
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance +50%</t>
+          <t>Bash resistance +50</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr"/>
@@ -14689,14 +13585,10 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr"/>
-      <c r="M278" s="2" t="inlineStr">
-        <is>
-          <t>Bash Res +50</t>
-        </is>
-      </c>
+      <c r="M278" s="2" t="inlineStr"/>
       <c r="N278" s="2" t="inlineStr">
         <is>
-          <t>agrees with dt22-wiki</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14731,7 +13623,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Bash resistance -50%</t>
+          <t>Bash resistance -50</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr"/>
@@ -14743,14 +13635,10 @@
       <c r="J279" s="2" t="inlineStr"/>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
-      <c r="M279" s="2" t="inlineStr">
-        <is>
-          <t>Bash Res -40</t>
-        </is>
-      </c>
+      <c r="M279" s="2" t="inlineStr"/>
       <c r="N279" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Bash resistance -50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14781,7 +13669,7 @@
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance +50%</t>
+          <t>Physical resistance +50</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr"/>
@@ -14797,14 +13685,10 @@
           <t>Slash, stab and bash</t>
         </is>
       </c>
-      <c r="M280" s="2" t="inlineStr">
-        <is>
-          <t>All Phys Res +30</t>
-        </is>
-      </c>
+      <c r="M280" s="2" t="inlineStr"/>
       <c r="N280" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance +50%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14839,7 +13723,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Physical resistance -20%</t>
+          <t>Physical resistance -20</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
@@ -14855,14 +13739,10 @@
           <t>Slash, stab and bash</t>
         </is>
       </c>
-      <c r="M281" s="2" t="inlineStr">
-        <is>
-          <t>All Phys Res -30</t>
-        </is>
-      </c>
+      <c r="M281" s="2" t="inlineStr"/>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>contradicts dt22-wiki (Physical resistance -20%)</t>
+          <t>unchanged</t>
         </is>
       </c>
     </row>
@@ -14877,7 +13757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -14898,110 +13778,50 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>earlier build: agrees with dt2-wiki</t>
+          <t>earlier build: unchanged</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>16</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>earlier build: agrees with dt22-wiki</t>
+          <t>figure already in the vanilla name</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>earlier build: contradicts dt2-wiki</t>
+          <t>figure from dt2-wiki</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>earlier build: contradicts dt22-wiki</t>
+          <t>figure from dt22-wiki</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>earlier build: figure without a source</t>
+          <t>no figure known (vanilla name kept)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>earlier build: reworded, no new figure</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>earlier build: unchanged</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>figure already in the vanilla name</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>figure from dt2-wiki</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>figure from dt22-wiki</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>no figure known (vanilla name kept)</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
         <v>101</v>
       </c>
     </row>

--- a/mod_project/data_tables/qol_enchant_text.xlsx
+++ b/mod_project/data_tables/qol_enchant_text.xlsx
@@ -667,14 +667,14 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>The DT2-2 wiki lists this one as unknown (-??%)</t>
+          <t>x86: 0x4f83b6 (-10% Max HP)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -2073,14 +2073,14 @@
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44b69a (mulss 4.0)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
@@ -2127,14 +2127,14 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44b6d4 (addss xmm0, xmm0)</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
@@ -2175,14 +2175,22 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Physical accuracy UP</t>
+          <t>Physical accuracy +4%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44ad18 (mulss 4.0)</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2221,14 +2229,22 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Physical accuracy MiniUP</t>
+          <t>Physical accuracy +2%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44ad52 (addss xmm0, xmm0)</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2267,14 +2283,22 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Physical defense UP</t>
+          <t>Physical defense +4%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44b8eb (mulss 4.0)</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2313,14 +2337,22 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Physical defense MiniUP</t>
+          <t>Physical defense +2%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44b925 (addss xmm0, xmm0)</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2359,14 +2391,22 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Physical evasion UP</t>
+          <t>Physical evasion +4%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44ad91 (mulss 4.0)</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2405,14 +2445,22 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Physical evasion MiniUP</t>
+          <t>Physical evasion +2%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44adcb (addss xmm0, xmm0)</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2457,14 +2505,14 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44df30 (mulss 4.0)</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
@@ -2511,14 +2559,14 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44df6a (addss xmm0, xmm0)</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
@@ -2559,14 +2607,22 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Magic accuracy UP</t>
+          <t>Magic accuracy +3%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d67b (mulss 3.0)</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2605,14 +2661,22 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Magic accuracy MiniUP</t>
+          <t>Magic accuracy +1%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d6bd (addss 1.0 flat)</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2651,14 +2715,22 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Magic defense UP</t>
+          <t>Magic defense +4%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44e5b1 (mulss 4.0)</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2697,14 +2769,22 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Magic defense MiniUP</t>
+          <t>Magic defense +2%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44e637 (addss xmm1, xmm1)</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2743,14 +2823,22 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Magic evasion UP</t>
+          <t>Magic evasion +3%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d6f0 (mulss 3.0)</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2789,14 +2877,22 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Magic evasion MiniUP</t>
+          <t>Magic evasion +1%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d742 (addss 1.0 flat)</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2835,14 +2931,22 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Critical rate UP</t>
+          <t>Critical rate +4%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44f357 (mulss 4.0)</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2881,14 +2985,22 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Critical rate MiniUP</t>
+          <t>Critical rate +1%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44f3f7 (addss 1.0 flat)</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2927,14 +3039,22 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Enemy critical rate DOWN</t>
+          <t>Enemy critical rate -4%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44f3c0 (mulss 4.0)</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2973,14 +3093,22 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Enemy critical rate MiniDOWN</t>
+          <t>Enemy critical rate -2%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44f43f (addss xmm0, xmm0)</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3019,18 +3147,22 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Enmity +5%</t>
+          <t>Enmity +10</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44a736 (flat +10 enmity points)</t>
+        </is>
+      </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3069,18 +3201,22 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Enmity -5%</t>
+          <t>Enmity -5</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44a74d (flat -5 enmity points)</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3125,14 +3261,14 @@
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>DT2-2 player test: only five of them count</t>
+          <t>x86: 0x44a114 (mulss 0.10)</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
@@ -3179,12 +3315,16 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44a14d (mulss 0.05)</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3223,14 +3363,22 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Speed DOWN</t>
+          <t>Speed -10%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44a185 (mulss 0.10)</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3275,14 +3423,14 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>DT2-2 player test: only three of them count</t>
+          <t>x86: 0x449f6a (mulss 0.20)</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
@@ -3329,12 +3477,16 @@
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x449fa3 (mulss 0.10)</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3373,14 +3525,22 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Chant speed DOWN</t>
+          <t>Chant speed -20%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x449fdb (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3419,14 +3579,22 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Interruption rate GrandDOWN</t>
+          <t>Interruption rate -10%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d083 (mulss 0.10)</t>
+        </is>
+      </c>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3471,12 +3639,16 @@
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d0bd (mulss 0.06)</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3521,12 +3693,16 @@
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d0f4 (mulss 0.03)</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3571,12 +3747,16 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d12b (mulss 0.06)</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3615,14 +3795,22 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Interruption rate MegaDOWN</t>
+          <t>Interruption rate -20%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44d166 (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3985,20 +4173,20 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Convert 5% of received damage into TP</t>
+          <t>Damage to TP: 5%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>First game: at least 1 TP, also from poison and traps</t>
+          <t>x86: 0x47e68d (mulss 0.05)</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
@@ -4039,14 +4227,22 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Convert received damage into big TP</t>
+          <t>Damage to TP: 10%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x47e6be (mulss 0.10)</t>
+        </is>
+      </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4091,14 +4287,14 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e04b (mulss 0.20)</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
@@ -4145,14 +4341,14 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e101 (mulss 0.20)</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr"/>
@@ -4199,14 +4395,14 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e1b7 (mulss 0.20)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
@@ -4253,14 +4449,14 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e26d (mulss 0.20)</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
@@ -4307,14 +4503,14 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e37d (mulss 0.20)</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
@@ -5931,14 +6127,14 @@
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Slash, stab and bash. The DT2-2 wiki lists this one as unknown (-??)</t>
+          <t>x86: 0x4f8b86 (-10 flat resistance)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr"/>
@@ -7483,20 +7679,20 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb HP (50% of damage)</t>
+          <t>Attacks absorb 50% HP</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x42156f (movss 0.50, no undead)</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr"/>
@@ -7537,20 +7733,20 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb HP (15% of damage)</t>
+          <t>Attacks absorb 15% HP</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x4215c4 (movss 0.15, no undead)</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr"/>
@@ -7587,20 +7783,20 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb TP (20% of damage)</t>
+          <t>Attacks absorb 20% TP</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x421619 (movss 0.20, no undead)</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr"/>
@@ -7641,20 +7837,20 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Normal attacks absorb TP (5% of damage)</t>
+          <t>Attacks absorb 5% TP</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x42166e (movss 0.05, no undead)</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr"/>
@@ -7737,20 +7933,20 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Demons +40%</t>
+          <t>Physical attack vs. Demons +30%</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44bfbb (mulss 0.30)</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr"/>
@@ -7791,20 +7987,20 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Demons +20%</t>
+          <t>Physical attack vs. Demons +15%</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44bff5 (mulss 0.15)</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr"/>
@@ -7841,20 +8037,20 @@
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Apparitions +40%</t>
+          <t>Physical attack vs. Apparitions +30%</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c06f (mulss 0.30)</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr"/>
@@ -7895,20 +8091,20 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Apparitions +20%</t>
+          <t>Physical attack vs. Apparitions +15%</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr"/>
@@ -7945,20 +8141,20 @@
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Phys. attack vs. Magic Beings +40%</t>
+          <t>Phys. attack vs. Magic Beings +30%</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c0ce (mulss 0.30)</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr"/>
@@ -7999,20 +8195,20 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Magic Beings +20%</t>
+          <t>Physical attack vs. Magic Beings +15%</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr"/>
@@ -8049,20 +8245,20 @@
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Humans +100%</t>
+          <t>Physical attack vs. Humans +60%</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x2</t>
+          <t>x86: 0x44c131 (mulss 0.60)</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr"/>
@@ -8099,20 +8295,20 @@
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Humans +40%</t>
+          <t>Physical attack vs. Humans +30%</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c16b (mulss 0.30)</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr"/>
@@ -8153,20 +8349,20 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Humans +20%</t>
+          <t>Physical attack vs. Humans +15%</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c1a5 (mulss 0.15)</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr"/>
@@ -8203,20 +8399,20 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Undead +40%</t>
+          <t>Physical attack vs. Undead +30%</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr"/>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c1e5 (mulss 0.30)</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr"/>
@@ -8257,20 +8453,20 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Undead +20%</t>
+          <t>Physical attack vs. Undead +15%</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr"/>
@@ -8307,20 +8503,20 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Dragons +40%</t>
+          <t>Physical attack vs. Dragons +30%</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c244 (mulss 0.30)</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr"/>
@@ -8361,20 +8557,20 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Dragons +20%</t>
+          <t>Physical attack vs. Dragons +15%</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr"/>
@@ -8411,20 +8607,20 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Beasts +40%</t>
+          <t>Physical attack vs. Beasts +30%</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c2a3 (mulss 0.30)</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr"/>
@@ -8465,20 +8661,20 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Beasts +20%</t>
+          <t>Physical attack vs. Beasts +15%</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr"/>
@@ -8521,14 +8717,14 @@
       <c r="H163" s="2" t="inlineStr"/>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr"/>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x2</t>
+          <t>x86: 0x44c32a (+1.0)</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr"/>
@@ -8575,14 +8771,14 @@
       <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.5</t>
+          <t>x86: 0x44c352 (mulss 0.50)</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr"/>
@@ -8793,14 +8989,14 @@
       <c r="H169" s="2" t="inlineStr"/>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr"/>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>First game: physical damage x2</t>
+          <t>x86: 0x44c3ab (+1.0)</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr"/>
@@ -8971,14 +9167,22 @@
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Demons MegaUP</t>
+          <t>Physical attack vs. Demons +60%</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J173" s="2" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c04d (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M173" s="2" t="inlineStr"/>
       <c r="N173" s="2" t="inlineStr">
         <is>
@@ -9013,14 +9217,22 @@
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Apparitions MegaUP</t>
+          <t>Physical attack vs. Apparitions +60%</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M174" s="2" t="inlineStr"/>
       <c r="N174" s="2" t="inlineStr">
         <is>
@@ -9055,14 +9267,22 @@
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Phys. attack vs. Magic Beings MegaUP</t>
+          <t>Phys. attack vs. Magic Beings +60%</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
-      <c r="I175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J175" s="2" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M175" s="2" t="inlineStr"/>
       <c r="N175" s="2" t="inlineStr">
         <is>
@@ -9097,14 +9317,22 @@
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Undead MegaUP</t>
+          <t>Physical attack vs. Undead +60%</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M176" s="2" t="inlineStr"/>
       <c r="N176" s="2" t="inlineStr">
         <is>
@@ -9139,14 +9367,22 @@
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Dragons MegaUP</t>
+          <t>Physical attack vs. Dragons +60%</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
-      <c r="I177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J177" s="2" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M177" s="2" t="inlineStr"/>
       <c r="N177" s="2" t="inlineStr">
         <is>
@@ -9181,14 +9417,22 @@
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>Physical attack vs. Beasts MegaUP</t>
+          <t>Physical attack vs. Beasts +60%</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M178" s="2" t="inlineStr"/>
       <c r="N178" s="2" t="inlineStr">
         <is>
@@ -9223,14 +9467,22 @@
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>Phys. attack vs. Sea Creatures MegaUP</t>
+          <t>Phys. attack vs. Sea Creatures +100%</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J179" s="2" t="inlineStr"/>
       <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c3ab (+1.0)</t>
+        </is>
+      </c>
       <c r="M179" s="2" t="inlineStr"/>
       <c r="N179" s="2" t="inlineStr">
         <is>
@@ -9265,14 +9517,22 @@
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Slightly reduce encounter rate</t>
+          <t>Encounter rate -1%</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc812 (-1 flat)</t>
+        </is>
+      </c>
       <c r="M180" s="2" t="inlineStr"/>
       <c r="N180" s="2" t="inlineStr">
         <is>
@@ -9307,14 +9567,22 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>Greatly reduce encounter rate</t>
+          <t>Encounter rate -2%</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr"/>
-      <c r="I181" s="2" t="inlineStr"/>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J181" s="2" t="inlineStr"/>
       <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc823 (-2 flat)</t>
+        </is>
+      </c>
       <c r="M181" s="2" t="inlineStr"/>
       <c r="N181" s="2" t="inlineStr">
         <is>
@@ -9349,14 +9617,22 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Slightly increase encounter rate</t>
+          <t>Encounter rate +1%</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr"/>
-      <c r="I182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J182" s="2" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc834 (+1 flat)</t>
+        </is>
+      </c>
       <c r="M182" s="2" t="inlineStr"/>
       <c r="N182" s="2" t="inlineStr">
         <is>
@@ -9391,14 +9667,22 @@
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Greatly increase encounter rate</t>
+          <t>Encounter rate +2%</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr"/>
-      <c r="I183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J183" s="2" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc843 (+2 flat)</t>
+        </is>
+      </c>
       <c r="M183" s="2" t="inlineStr"/>
       <c r="N183" s="2" t="inlineStr">
         <is>
@@ -9517,14 +9801,22 @@
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Attack vs. high lvl enemies UP</t>
+          <t>Attack vs. high lvl enemies +10%</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
-      <c r="I186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44ca0b (mulss 0.10)</t>
+        </is>
+      </c>
       <c r="M186" s="2" t="inlineStr"/>
       <c r="N186" s="2" t="inlineStr">
         <is>
@@ -9559,14 +9851,22 @@
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Attack vs. low lvl enemies UP</t>
+          <t>Attack vs. low lvl enemies +10%</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J187" s="2" t="inlineStr"/>
       <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44ca60 (mulss 0.10)</t>
+        </is>
+      </c>
       <c r="M187" s="2" t="inlineStr"/>
       <c r="N187" s="2" t="inlineStr">
         <is>
@@ -10525,14 +10825,22 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>TP Cost for techniques DOWN</t>
+          <t>TP Cost for techniques -20%</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
-      <c r="I210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J210" s="2" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr"/>
-      <c r="L210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd2a7 (mulss 0.80)</t>
+        </is>
+      </c>
       <c r="M210" s="2" t="inlineStr"/>
       <c r="N210" s="2" t="inlineStr">
         <is>
@@ -10567,14 +10875,22 @@
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>TP Cost for techniques MegaDOWN</t>
+          <t>TP Cost for techniques -40%</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J211" s="2" t="inlineStr"/>
       <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd31e (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M211" s="2" t="inlineStr"/>
       <c r="N211" s="2" t="inlineStr">
         <is>
@@ -10609,14 +10925,22 @@
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>TP Cost for spells DOWN</t>
+          <t>TP Cost for spells -20%</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J212" s="2" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd2f8 (mulss 0.80)</t>
+        </is>
+      </c>
       <c r="M212" s="2" t="inlineStr"/>
       <c r="N212" s="2" t="inlineStr">
         <is>
@@ -10651,14 +10975,22 @@
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>TP Cost for spells MegaDOWN</t>
+          <t>TP Cost for spells -40%</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr"/>
-      <c r="I213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J213" s="2" t="inlineStr"/>
       <c r="K213" s="2" t="inlineStr"/>
-      <c r="L213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd31e (mulss 0.60)</t>
+        </is>
+      </c>
       <c r="M213" s="2" t="inlineStr"/>
       <c r="N213" s="2" t="inlineStr">
         <is>
@@ -10693,14 +11025,22 @@
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>Fire attack for both sides UP</t>
+          <t>Fire attack for both sides +20%</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr"/>
-      <c r="I214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr"/>
-      <c r="L214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M214" s="2" t="inlineStr"/>
       <c r="N214" s="2" t="inlineStr">
         <is>
@@ -10735,14 +11075,22 @@
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Water attack for both sides UP</t>
+          <t>Water attack for both sides +20%</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J215" s="2" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
-      <c r="L215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M215" s="2" t="inlineStr"/>
       <c r="N215" s="2" t="inlineStr">
         <is>
@@ -10777,14 +11125,22 @@
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Wind attack for both sides UP</t>
+          <t>Wind attack for both sides +20%</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
-      <c r="I216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr"/>
-      <c r="L216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M216" s="2" t="inlineStr"/>
       <c r="N216" s="2" t="inlineStr">
         <is>
@@ -10819,14 +11175,22 @@
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Earth attack for both sides UP</t>
+          <t>Earth attack for both sides +20%</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J217" s="2" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
-      <c r="L217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M217" s="2" t="inlineStr"/>
       <c r="N217" s="2" t="inlineStr">
         <is>
@@ -10861,14 +11225,22 @@
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Lightning attack for both sides UP</t>
+          <t>Lightning attack for both sides +20%</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J218" s="2" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr"/>
-      <c r="L218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M218" s="2" t="inlineStr"/>
       <c r="N218" s="2" t="inlineStr">
         <is>
@@ -10995,14 +11367,22 @@
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Higher chance of shop encounters</t>
+          <t>Shop encounters: steps -50%</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
-      <c r="I221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J221" s="2" t="inlineStr"/>
       <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x5563b3 (steps counter 50-&gt;25)</t>
+        </is>
+      </c>
       <c r="M221" s="2" t="inlineStr"/>
       <c r="N221" s="2" t="inlineStr">
         <is>
@@ -11079,14 +11459,22 @@
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>Damage of joint skills UP</t>
+          <t>Damage of joint skills +10%</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J223" s="2" t="inlineStr"/>
       <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c8b4 (mulss 0.10)</t>
+        </is>
+      </c>
       <c r="M223" s="2" t="inlineStr"/>
       <c r="N223" s="2" t="inlineStr">
         <is>
@@ -11247,14 +11635,22 @@
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Rate of status ailments dissipation UP</t>
+          <t>Ailment recovery: 2 turns</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr"/>
-      <c r="I227" s="2" t="inlineStr"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J227" s="2" t="inlineStr"/>
       <c r="K227" s="2" t="inlineStr"/>
-      <c r="L227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x48d202 (ailment threshold 2 turns)</t>
+        </is>
+      </c>
       <c r="M227" s="2" t="inlineStr"/>
       <c r="N227" s="2" t="inlineStr">
         <is>
@@ -11381,14 +11777,22 @@
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Critical rate UP</t>
+          <t>Min Critical rate: 20%</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
-      <c r="I230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J230" s="2" t="inlineStr"/>
       <c r="K230" s="2" t="inlineStr"/>
-      <c r="L230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44f4c3 (crit floor 20%)</t>
+        </is>
+      </c>
       <c r="M230" s="2" t="inlineStr"/>
       <c r="N230" s="2" t="inlineStr">
         <is>
@@ -11557,14 +11961,22 @@
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Reduce damage penalty for missed spells</t>
+          <t>Missed spell penalty: 25%</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr"/>
-      <c r="I234" s="2" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J234" s="2" t="inlineStr"/>
       <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44ee4e (75% dmg on miss)</t>
+        </is>
+      </c>
       <c r="M234" s="2" t="inlineStr"/>
       <c r="N234" s="2" t="inlineStr">
         <is>
@@ -11599,14 +12011,22 @@
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Double EXP</t>
+          <t>Double EXP (+100%)</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr"/>
-      <c r="I235" s="2" t="inlineStr"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J235" s="2" t="inlineStr"/>
       <c r="K235" s="2" t="inlineStr"/>
-      <c r="L235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x445a1e (x2.0 EXP)</t>
+        </is>
+      </c>
       <c r="M235" s="2" t="inlineStr"/>
       <c r="N235" s="2" t="inlineStr">
         <is>
@@ -11645,14 +12065,22 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Equipment drop rate UP</t>
+          <t>Equipment drop rate +20%</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J236" s="2" t="inlineStr"/>
       <c r="K236" s="2" t="inlineStr"/>
-      <c r="L236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x558255 (+20 drop rate)</t>
+        </is>
+      </c>
       <c r="M236" s="2" t="inlineStr"/>
       <c r="N236" s="2" t="inlineStr">
         <is>
@@ -11687,14 +12115,22 @@
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Damage to enemies with status ailments UP</t>
+          <t>Damage to enemies with status ailments +15%</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr"/>
-      <c r="I237" s="2" t="inlineStr"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J237" s="2" t="inlineStr"/>
       <c r="K237" s="2" t="inlineStr"/>
-      <c r="L237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44cd83 (mulss 0.15)</t>
+        </is>
+      </c>
       <c r="M237" s="2" t="inlineStr"/>
       <c r="N237" s="2" t="inlineStr">
         <is>
@@ -11771,14 +12207,22 @@
       <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Joint skill damage MegaUP</t>
+          <t>Joint skill damage +20%</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr"/>
-      <c r="I239" s="2" t="inlineStr"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J239" s="2" t="inlineStr"/>
       <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44c8ee (mulss 0.20)</t>
+        </is>
+      </c>
       <c r="M239" s="2" t="inlineStr"/>
       <c r="N239" s="2" t="inlineStr">
         <is>
@@ -11813,14 +12257,22 @@
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Increase Mimic appearance rate in chests</t>
+          <t>Mimic chest rate +20%</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
-      <c r="I240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J240" s="2" t="inlineStr"/>
       <c r="K240" s="2" t="inlineStr"/>
-      <c r="L240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x55577a (+20% mimic chance)</t>
+        </is>
+      </c>
       <c r="M240" s="2" t="inlineStr"/>
       <c r="N240" s="2" t="inlineStr">
         <is>
@@ -12023,14 +12475,22 @@
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>May rarely recover all HP when turn starts</t>
+          <t>4% chance: full HP on turn</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr"/>
-      <c r="I245" s="2" t="inlineStr"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J245" s="2" t="inlineStr"/>
       <c r="K245" s="2" t="inlineStr"/>
-      <c r="L245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x437d1a (4% full HP on turn)</t>
+        </is>
+      </c>
       <c r="M245" s="2" t="inlineStr"/>
       <c r="N245" s="2" t="inlineStr">
         <is>
@@ -12107,14 +12567,22 @@
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Magic incantations go very fast... sometimes</t>
+          <t>Chant speed +25%</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr"/>
-      <c r="I247" s="2" t="inlineStr"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J247" s="2" t="inlineStr"/>
       <c r="K247" s="2" t="inlineStr"/>
-      <c r="L247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44a380 (+25% chant speed)</t>
+        </is>
+      </c>
       <c r="M247" s="2" t="inlineStr"/>
       <c r="N247" s="2" t="inlineStr">
         <is>
@@ -12257,14 +12725,22 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Dance skill efficacy UP</t>
+          <t>Dance skill efficacy +2%</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr"/>
-      <c r="I250" s="2" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="2" t="inlineStr"/>
-      <c r="L250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x48c04a (mulss 0.02)</t>
+        </is>
+      </c>
       <c r="M250" s="2" t="inlineStr"/>
       <c r="N250" s="2" t="inlineStr">
         <is>
@@ -12299,14 +12775,22 @@
       <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Dance skill efficacy UP</t>
+          <t>Dance skill efficacy +1%</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr"/>
-      <c r="I251" s="2" t="inlineStr"/>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J251" s="2" t="inlineStr"/>
       <c r="K251" s="2" t="inlineStr"/>
-      <c r="L251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x48c07e (mulss 0.01)</t>
+        </is>
+      </c>
       <c r="M251" s="2" t="inlineStr"/>
       <c r="N251" s="2" t="inlineStr">
         <is>
@@ -12345,14 +12829,22 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Doll skill efficacy UP</t>
+          <t>Doll skill efficacy +2%</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr"/>
-      <c r="I252" s="2" t="inlineStr"/>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J252" s="2" t="inlineStr"/>
       <c r="K252" s="2" t="inlineStr"/>
-      <c r="L252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44b533 (mulss 0.02)</t>
+        </is>
+      </c>
       <c r="M252" s="2" t="inlineStr"/>
       <c r="N252" s="2" t="inlineStr">
         <is>
@@ -12387,14 +12879,22 @@
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Doll skill efficacy MiniUP</t>
+          <t>Doll skill efficacy +1%</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr"/>
-      <c r="I253" s="2" t="inlineStr"/>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
       <c r="J253" s="2" t="inlineStr"/>
       <c r="K253" s="2" t="inlineStr"/>
-      <c r="L253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>x86: 0x44b58e (mulss 0.01)</t>
+        </is>
+      </c>
       <c r="M253" s="2" t="inlineStr"/>
       <c r="N253" s="2" t="inlineStr">
         <is>
@@ -13798,21 +14298,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>figure from dt2-wiki</t>
+          <t>figure from dt22-wiki</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>figure from dt22-wiki</t>
+          <t>figure from exe-verified</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -13822,7 +14322,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>101</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -13836,7 +14336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="2" max="2"/>
@@ -13888,6 +14388,23 @@
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Directly decompiled from DT2-2 unwrapped x86 executable</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
